--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6E5BA1-D2C3-1243-9D0B-A29AC05E5591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C72583-3C19-3E42-A4C8-298823DB421F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19660" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-8880" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="356">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1072,16 +1072,43 @@
   </si>
   <si>
     <t>页脚文字</t>
+  </si>
+  <si>
+    <t>FILM-0020</t>
+  </si>
+  <si>
+    <t>Frence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franch,English </t>
+  </si>
+  <si>
+    <t>89 min</t>
+  </si>
+  <si>
+    <t>Jean-Michel Carré</t>
+  </si>
+  <si>
+    <t>Ilya Tolstoy;Brooke Dolan</t>
+  </si>
+  <si>
+    <t>Gangtok, Gyangtse, Lhasa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1549,7 +1576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -2262,19 +2289,13 @@
         <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
       </c>
-      <c r="I13" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" t="s">
-        <v>1</v>
-      </c>
       <c r="K13" t="s">
-        <v>1</v>
+        <v>354</v>
       </c>
       <c r="L13" t="s">
         <v>117</v>
@@ -2286,7 +2307,7 @@
         <v>54</v>
       </c>
       <c r="O13" t="s">
-        <v>1</v>
+        <v>355</v>
       </c>
       <c r="P13" t="s">
         <v>118</v>
@@ -2690,10 +2711,40 @@
         <v>1</v>
       </c>
     </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>349</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21">
+        <v>2024</v>
+      </c>
+      <c r="E21" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>353</v>
+      </c>
+      <c r="M21" t="s">
+        <v>350</v>
+      </c>
+      <c r="N21" t="s">
+        <v>351</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R20" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R12 A14:R20 A13:F13 H13 L13:N13 P13:R13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C72583-3C19-3E42-A4C8-298823DB421F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBC9CFD-5452-6648-AC45-52333F35361D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-8880" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-8280" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="358">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1080,9 +1080,6 @@
     <t>Frence</t>
   </si>
   <si>
-    <t xml:space="preserve">Franch,English </t>
-  </si>
-  <si>
     <t>89 min</t>
   </si>
   <si>
@@ -1093,6 +1090,15 @@
   </si>
   <si>
     <t>Gangtok, Gyangtse, Lhasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franch;English </t>
+  </si>
+  <si>
+    <t>United Kingdom: March 20, 2024</t>
+  </si>
+  <si>
+    <t>PERSON-0042</t>
   </si>
 </sst>
 </file>
@@ -2295,7 +2301,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L13" t="s">
         <v>117</v>
@@ -2307,7 +2313,7 @@
         <v>54</v>
       </c>
       <c r="O13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P13" t="s">
         <v>118</v>
@@ -2722,7 +2728,7 @@
         <v>2024</v>
       </c>
       <c r="E21" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F21" t="s">
         <v>51</v>
@@ -2731,13 +2737,16 @@
         <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>353</v>
+        <v>352</v>
+      </c>
+      <c r="L21" t="s">
+        <v>356</v>
       </c>
       <c r="M21" t="s">
         <v>350</v>
       </c>
       <c r="N21" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -2751,7 +2760,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
@@ -3982,7 +3991,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>357</v>
+      </c>
+      <c r="B43" t="s">
+        <v>352</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:I20 A22:I42 A21:D21 H21:I21" numberStoredAsText="1"/>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBC9CFD-5452-6648-AC45-52333F35361D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72E5F1E-2676-A749-BD57-37DC2A6AD5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-8280" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="363">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1099,6 +1099,21 @@
   </si>
   <si>
     <t>PERSON-0042</t>
+  </si>
+  <si>
+    <t>Ilya Tolstoy</t>
+  </si>
+  <si>
+    <t>Brooke Dolan</t>
+  </si>
+  <si>
+    <t>PERSON-0043</t>
+  </si>
+  <si>
+    <t>PERSON-0044</t>
+  </si>
+  <si>
+    <t>American</t>
   </si>
 </sst>
 </file>
@@ -2760,7 +2775,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
@@ -4000,6 +4015,46 @@
       </c>
       <c r="D43" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>360</v>
+      </c>
+      <c r="B44" t="s">
+        <v>358</v>
+      </c>
+      <c r="D44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44">
+        <v>1903</v>
+      </c>
+      <c r="F44">
+        <v>1970</v>
+      </c>
+      <c r="G44" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>361</v>
+      </c>
+      <c r="B45" t="s">
+        <v>359</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45">
+        <v>1908</v>
+      </c>
+      <c r="F45">
+        <v>1945</v>
+      </c>
+      <c r="G45" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72E5F1E-2676-A749-BD57-37DC2A6AD5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AE3E1C-6EEA-3F41-8CB3-08916F7D325E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-8280" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32700" yWindow="-7260" windowWidth="41180" windowHeight="12740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="461">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1114,13 +1114,307 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Cesta vede do Tibetu</t>
+  </si>
+  <si>
+    <t>The Road Leads to Tibet</t>
+  </si>
+  <si>
+    <t>Czechoslovakia</t>
+  </si>
+  <si>
+    <t>The Great Unity of China's Ethnic Groups</t>
+  </si>
+  <si>
+    <t>中国民族大团结</t>
+  </si>
+  <si>
+    <t>中央代表团访问西藏</t>
+  </si>
+  <si>
+    <t>The Central Delegation Visits Tibet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">从拉萨到北京 </t>
+  </si>
+  <si>
+    <t>From Lhasa to Beijing</t>
+  </si>
+  <si>
+    <t>Light Radiates Upon Tibet</t>
+  </si>
+  <si>
+    <t>光明照耀着西藏</t>
+  </si>
+  <si>
+    <t>农奴</t>
+  </si>
+  <si>
+    <t>The serf</t>
+  </si>
+  <si>
+    <t>千里迢迢探亲人</t>
+  </si>
+  <si>
+    <t>庆祝西藏自治区成立</t>
+  </si>
+  <si>
+    <t>A Journey of Thousands of Miles to Visit Loved Ones</t>
+  </si>
+  <si>
+    <t>Celebrating the Establishment of the Tibet Autonomous Region</t>
+  </si>
+  <si>
+    <t>春到拉萨</t>
+  </si>
+  <si>
+    <t>Spring Comes to Lhasa</t>
+  </si>
+  <si>
+    <t>春到西藏</t>
+  </si>
+  <si>
+    <t>Spring Comes to Tibet</t>
+  </si>
+  <si>
+    <t>民族万岁</t>
+  </si>
+  <si>
+    <t>Zheng Junli</t>
+  </si>
+  <si>
+    <t>郑君里</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>China: 1940</t>
+  </si>
+  <si>
+    <t>Long Live the Nation</t>
+  </si>
+  <si>
+    <t>Song of Zhumulangma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珠穆朗玛之歌 </t>
+  </si>
+  <si>
+    <t>百万农奴站起来</t>
+  </si>
+  <si>
+    <t>Million Serfs Stood Up</t>
+  </si>
+  <si>
+    <t>Tibet's Serf System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">西藏的农奴制度 </t>
+  </si>
+  <si>
+    <t>西藏致敬团</t>
+  </si>
+  <si>
+    <t>The Tibetan Tribute Delegation</t>
+  </si>
+  <si>
+    <t>通向拉萨的幸福道路</t>
+  </si>
+  <si>
+    <t>Happy Road to Lhasa</t>
+  </si>
+  <si>
+    <t>FILM-0021</t>
+  </si>
+  <si>
+    <t>FILM-0022</t>
+  </si>
+  <si>
+    <t>FILM-0023</t>
+  </si>
+  <si>
+    <t>FILM-0024</t>
+  </si>
+  <si>
+    <t>FILM-0025</t>
+  </si>
+  <si>
+    <t>FILM-0026</t>
+  </si>
+  <si>
+    <t>FILM-0027</t>
+  </si>
+  <si>
+    <t>FILM-0028</t>
+  </si>
+  <si>
+    <t>FILM-0029</t>
+  </si>
+  <si>
+    <t>FILM-0030</t>
+  </si>
+  <si>
+    <t>FILM-0031</t>
+  </si>
+  <si>
+    <t>FILM-0032</t>
+  </si>
+  <si>
+    <t>FILM-0033</t>
+  </si>
+  <si>
+    <t>FILM-0034</t>
+  </si>
+  <si>
+    <t>FILM-0035</t>
+  </si>
+  <si>
+    <t>FILM-0036</t>
+  </si>
+  <si>
+    <t>53 min</t>
+  </si>
+  <si>
+    <t>Chen Feng</t>
+  </si>
+  <si>
+    <t>晨烽</t>
+  </si>
+  <si>
+    <t>Beijing Film Studio</t>
+  </si>
+  <si>
+    <t>中央电影局北京电影制片厂</t>
+  </si>
+  <si>
+    <t>中央新闻纪录电影制片厂</t>
+  </si>
+  <si>
+    <t>Central Newsreel and Documentary Film Studio</t>
+  </si>
+  <si>
+    <t>Beijing Film Studio;Central Newsreel and Documentary Film Studio</t>
+  </si>
+  <si>
+    <t>Hao Yusheng;Jiang Tao</t>
+  </si>
+  <si>
+    <t>Hao Yusheng</t>
+  </si>
+  <si>
+    <t>Jiang Tao</t>
+  </si>
+  <si>
+    <t>郝玉生</t>
+  </si>
+  <si>
+    <t>江涛</t>
+  </si>
+  <si>
+    <t>57 min</t>
+  </si>
+  <si>
+    <t>Hu Qi;Vladimír Sís</t>
+  </si>
+  <si>
+    <t>Vladimír Sís;Hu Qi</t>
+  </si>
+  <si>
+    <t>Hu Qi</t>
+  </si>
+  <si>
+    <t>Vladimír Sís</t>
+  </si>
+  <si>
+    <t>胡奇</t>
+  </si>
+  <si>
+    <t>Bayi Film Studio</t>
+  </si>
+  <si>
+    <t>八一电影制片厂</t>
+  </si>
+  <si>
+    <t>月明电影公司</t>
+  </si>
+  <si>
+    <t>Colorful Road</t>
+  </si>
+  <si>
+    <t>五彩路</t>
+  </si>
+  <si>
+    <t>88 min</t>
+  </si>
+  <si>
+    <t>Wei Rong</t>
+  </si>
+  <si>
+    <t>魏荣</t>
+  </si>
+  <si>
+    <t>Kang Yujie</t>
+  </si>
+  <si>
+    <t>Huang Zongjiang</t>
+  </si>
+  <si>
+    <t>Beijing Science and Educational Film Studio</t>
+  </si>
+  <si>
+    <t>北京科学教育电影制片厂</t>
+  </si>
+  <si>
+    <t>黄宗江</t>
+  </si>
+  <si>
+    <t>康玉洁</t>
+  </si>
+  <si>
+    <t>Li Jun</t>
+  </si>
+  <si>
+    <t>李俊</t>
+  </si>
+  <si>
+    <t>PERSON-0045</t>
+  </si>
+  <si>
+    <t>PERSON-0046</t>
+  </si>
+  <si>
+    <t>PERSON-0047</t>
+  </si>
+  <si>
+    <t>PERSON-0048</t>
+  </si>
+  <si>
+    <t>PERSON-0049</t>
+  </si>
+  <si>
+    <t>PERSON-0050</t>
+  </si>
+  <si>
+    <t>PERSON-0051</t>
+  </si>
+  <si>
+    <t>PERSON-0052</t>
+  </si>
+  <si>
+    <t>PERSON-0053</t>
+  </si>
+  <si>
+    <t>PERSON-0054</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1130,6 +1424,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1155,8 +1457,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1597,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -2354,7 +2657,7 @@
         <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>1</v>
+        <v>416</v>
       </c>
       <c r="F14" t="s">
         <v>51</v>
@@ -2366,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>1</v>
+        <v>417</v>
       </c>
       <c r="J14" t="s">
-        <v>1</v>
+        <v>417</v>
       </c>
       <c r="K14" t="s">
         <v>1</v>
@@ -2387,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>1</v>
+        <v>423</v>
       </c>
       <c r="Q14" t="s">
         <v>1</v>
@@ -2762,20 +3065,456 @@
       </c>
       <c r="N21" t="s">
         <v>355</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>400</v>
+      </c>
+      <c r="B22" t="s">
+        <v>364</v>
+      </c>
+      <c r="C22" t="s">
+        <v>363</v>
+      </c>
+      <c r="D22">
+        <v>1956</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M22" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>401</v>
+      </c>
+      <c r="B23" t="s">
+        <v>366</v>
+      </c>
+      <c r="C23" t="s">
+        <v>367</v>
+      </c>
+      <c r="D23">
+        <v>1950</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="M23" t="s">
+        <v>79</v>
+      </c>
+      <c r="N23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>402</v>
+      </c>
+      <c r="B24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24" t="s">
+        <v>368</v>
+      </c>
+      <c r="D24">
+        <v>1956</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" t="s">
+        <v>79</v>
+      </c>
+      <c r="N24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>403</v>
+      </c>
+      <c r="B25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" t="s">
+        <v>370</v>
+      </c>
+      <c r="D25">
+        <v>1955</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" t="s">
+        <v>79</v>
+      </c>
+      <c r="N25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>404</v>
+      </c>
+      <c r="B26" t="s">
+        <v>372</v>
+      </c>
+      <c r="C26" t="s">
+        <v>373</v>
+      </c>
+      <c r="D26">
+        <v>1952</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" t="s">
+        <v>424</v>
+      </c>
+      <c r="J26" t="s">
+        <v>424</v>
+      </c>
+      <c r="M26" t="s">
+        <v>79</v>
+      </c>
+      <c r="N26" t="s">
+        <v>123</v>
+      </c>
+      <c r="P26" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>405</v>
+      </c>
+      <c r="B27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C27" t="s">
+        <v>374</v>
+      </c>
+      <c r="D27">
+        <v>1963</v>
+      </c>
+      <c r="E27" t="s">
+        <v>440</v>
+      </c>
+      <c r="F27" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" t="s">
+        <v>449</v>
+      </c>
+      <c r="J27" t="s">
+        <v>444</v>
+      </c>
+      <c r="M27" t="s">
+        <v>79</v>
+      </c>
+      <c r="N27" t="s">
+        <v>123</v>
+      </c>
+      <c r="P27" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>406</v>
+      </c>
+      <c r="B28" t="s">
+        <v>378</v>
+      </c>
+      <c r="C28" t="s">
+        <v>376</v>
+      </c>
+      <c r="D28">
+        <v>1957</v>
+      </c>
+      <c r="M28" t="s">
+        <v>79</v>
+      </c>
+      <c r="N28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>407</v>
+      </c>
+      <c r="B29" t="s">
+        <v>379</v>
+      </c>
+      <c r="C29" t="s">
+        <v>377</v>
+      </c>
+      <c r="D29">
+        <v>1965</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="M29" t="s">
+        <v>79</v>
+      </c>
+      <c r="N29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>408</v>
+      </c>
+      <c r="B30" t="s">
+        <v>381</v>
+      </c>
+      <c r="C30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D30">
+        <v>1956</v>
+      </c>
+      <c r="M30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>409</v>
+      </c>
+      <c r="B31" t="s">
+        <v>383</v>
+      </c>
+      <c r="C31" t="s">
+        <v>382</v>
+      </c>
+      <c r="D31">
+        <v>1956</v>
+      </c>
+      <c r="M31" t="s">
+        <v>79</v>
+      </c>
+      <c r="N31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>410</v>
+      </c>
+      <c r="B32" t="s">
+        <v>389</v>
+      </c>
+      <c r="C32" t="s">
+        <v>384</v>
+      </c>
+      <c r="D32">
+        <v>1939</v>
+      </c>
+      <c r="E32" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" t="s">
+        <v>385</v>
+      </c>
+      <c r="L32" t="s">
+        <v>388</v>
+      </c>
+      <c r="M32" t="s">
+        <v>79</v>
+      </c>
+      <c r="N32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>411</v>
+      </c>
+      <c r="B33" t="s">
+        <v>390</v>
+      </c>
+      <c r="C33" t="s">
+        <v>391</v>
+      </c>
+      <c r="D33">
+        <v>1958</v>
+      </c>
+      <c r="M33" t="s">
+        <v>79</v>
+      </c>
+      <c r="N33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>412</v>
+      </c>
+      <c r="B34" t="s">
+        <v>393</v>
+      </c>
+      <c r="C34" t="s">
+        <v>392</v>
+      </c>
+      <c r="D34">
+        <v>1959</v>
+      </c>
+      <c r="M34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>413</v>
+      </c>
+      <c r="B35" t="s">
+        <v>394</v>
+      </c>
+      <c r="C35" t="s">
+        <v>395</v>
+      </c>
+      <c r="D35">
+        <v>1961</v>
+      </c>
+      <c r="F35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" t="s">
+        <v>443</v>
+      </c>
+      <c r="J35" t="s">
+        <v>444</v>
+      </c>
+      <c r="M35" t="s">
+        <v>79</v>
+      </c>
+      <c r="N35" t="s">
+        <v>123</v>
+      </c>
+      <c r="P35" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>414</v>
+      </c>
+      <c r="B36" t="s">
+        <v>397</v>
+      </c>
+      <c r="C36" t="s">
+        <v>396</v>
+      </c>
+      <c r="D36">
+        <v>1953</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="M36" t="s">
+        <v>79</v>
+      </c>
+      <c r="N36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>415</v>
+      </c>
+      <c r="B37" t="s">
+        <v>399</v>
+      </c>
+      <c r="C37" t="s">
+        <v>398</v>
+      </c>
+      <c r="D37">
+        <v>1956</v>
+      </c>
+      <c r="E37" t="s">
+        <v>429</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" t="s">
+        <v>430</v>
+      </c>
+      <c r="M37" t="s">
+        <v>79</v>
+      </c>
+      <c r="N37" t="s">
+        <v>123</v>
+      </c>
+      <c r="P37" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>438</v>
+      </c>
+      <c r="C38" t="s">
+        <v>439</v>
+      </c>
+      <c r="D38">
+        <v>1955</v>
+      </c>
+      <c r="E38" t="s">
+        <v>440</v>
+      </c>
+      <c r="F38" t="s">
+        <v>38</v>
+      </c>
+      <c r="I38" t="s">
+        <v>441</v>
+      </c>
+      <c r="J38" t="s">
+        <v>432</v>
+      </c>
+      <c r="M38" t="s">
+        <v>79</v>
+      </c>
+      <c r="N38" t="s">
+        <v>123</v>
+      </c>
+      <c r="P38" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R12 A14:R20 A13:F13 H13 L13:N13 P13:R13" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R12 A15:R20 A13:F13 H13 L13:N13 P13:R13 A14:D14 F14:H14 K14:O14 Q14:R14" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
@@ -4057,6 +4796,173 @@
         <v>362</v>
       </c>
     </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>451</v>
+      </c>
+      <c r="B46" t="s">
+        <v>385</v>
+      </c>
+      <c r="C46" t="s">
+        <v>386</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>452</v>
+      </c>
+      <c r="B47" t="s">
+        <v>417</v>
+      </c>
+      <c r="C47" t="s">
+        <v>418</v>
+      </c>
+      <c r="D47" t="s">
+        <v>194</v>
+      </c>
+      <c r="G47" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>453</v>
+      </c>
+      <c r="B48" t="s">
+        <v>425</v>
+      </c>
+      <c r="C48" t="s">
+        <v>427</v>
+      </c>
+      <c r="D48" t="s">
+        <v>194</v>
+      </c>
+      <c r="G48" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>454</v>
+      </c>
+      <c r="B49" t="s">
+        <v>426</v>
+      </c>
+      <c r="C49" t="s">
+        <v>428</v>
+      </c>
+      <c r="D49" t="s">
+        <v>194</v>
+      </c>
+      <c r="G49" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>455</v>
+      </c>
+      <c r="B50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C50" t="s">
+        <v>434</v>
+      </c>
+      <c r="D50" t="s">
+        <v>194</v>
+      </c>
+      <c r="G50" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B51" t="s">
+        <v>433</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>457</v>
+      </c>
+      <c r="B52" t="s">
+        <v>441</v>
+      </c>
+      <c r="C52" t="s">
+        <v>442</v>
+      </c>
+      <c r="D52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>458</v>
+      </c>
+      <c r="B53" t="s">
+        <v>443</v>
+      </c>
+      <c r="C53" t="s">
+        <v>448</v>
+      </c>
+      <c r="D53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>459</v>
+      </c>
+      <c r="B54" t="s">
+        <v>444</v>
+      </c>
+      <c r="C54" t="s">
+        <v>447</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>460</v>
+      </c>
+      <c r="B55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C55" t="s">
+        <v>450</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D58" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4068,7 +4974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -4134,10 +5040,10 @@
         <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>437</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -4471,10 +5377,45 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>419</v>
+      </c>
+      <c r="C18" t="s">
+        <v>420</v>
+      </c>
+      <c r="D18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>422</v>
+      </c>
+      <c r="C19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>435</v>
+      </c>
+      <c r="C20" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>445</v>
+      </c>
+      <c r="C21" t="s">
+        <v>446</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G17" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G2 A4:G17 A3:B3 E3:G3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AE3E1C-6EEA-3F41-8CB3-08916F7D325E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07206204-A025-6F49-AEB9-6731F307C395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32700" yWindow="-7260" windowWidth="41180" windowHeight="12740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-7260" windowWidth="38400" windowHeight="12740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="505">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1408,13 +1408,145 @@
   </si>
   <si>
     <t>PERSON-0054</t>
+  </si>
+  <si>
+    <t>FILM-0037</t>
+  </si>
+  <si>
+    <t>136 min</t>
+  </si>
+  <si>
+    <t>Jean-Jacques Annaud</t>
+  </si>
+  <si>
+    <t>Heinrich Harrer</t>
+  </si>
+  <si>
+    <t>Becky Johnston</t>
+  </si>
+  <si>
+    <t>Brad Pitt</t>
+  </si>
+  <si>
+    <t>David Thewlis</t>
+  </si>
+  <si>
+    <t>BD Wong</t>
+  </si>
+  <si>
+    <t>Heinrich Harrer;Becky Johnston</t>
+  </si>
+  <si>
+    <t>Brad Pitt;David Thewlis;BD Wong</t>
+  </si>
+  <si>
+    <t>United States: October 10, 1997</t>
+  </si>
+  <si>
+    <t>English;German;Mandarin;Tibetan;Hindi</t>
+  </si>
+  <si>
+    <t>Mandalay Entertainment</t>
+  </si>
+  <si>
+    <t>ORG-0017</t>
+  </si>
+  <si>
+    <t>ORG-0018</t>
+  </si>
+  <si>
+    <t>ORG-0019</t>
+  </si>
+  <si>
+    <t>ORG-0020</t>
+  </si>
+  <si>
+    <t>ORG-0021</t>
+  </si>
+  <si>
+    <t>FILM-0038</t>
+  </si>
+  <si>
+    <t>Seven League Productions</t>
+  </si>
+  <si>
+    <t>Mary Beales;George Campey;Heinrich Harrer</t>
+  </si>
+  <si>
+    <t>Mary Beales</t>
+  </si>
+  <si>
+    <t>George Campey</t>
+  </si>
+  <si>
+    <t>Writer;Cast</t>
+  </si>
+  <si>
+    <t>Heinrich Harrer;Peter Aufschnaiter;The Dalai Lama</t>
+  </si>
+  <si>
+    <t>The Dalai Lama</t>
+  </si>
+  <si>
+    <t>Peter Aufschnaiter</t>
+  </si>
+  <si>
+    <t>Casr</t>
+  </si>
+  <si>
+    <t>PERSON-0055</t>
+  </si>
+  <si>
+    <t>PERSON-0056</t>
+  </si>
+  <si>
+    <t>PERSON-0057</t>
+  </si>
+  <si>
+    <t>PERSON-0058</t>
+  </si>
+  <si>
+    <t>PERSON-0059</t>
+  </si>
+  <si>
+    <t>PERSON-0060</t>
+  </si>
+  <si>
+    <t>PERSON-0061</t>
+  </si>
+  <si>
+    <t>PERSON-0062</t>
+  </si>
+  <si>
+    <t>PERSON-0064</t>
+  </si>
+  <si>
+    <t>PERSON-0065</t>
+  </si>
+  <si>
+    <t>Tibetan</t>
+  </si>
+  <si>
+    <t>ORG-0022</t>
+  </si>
+  <si>
+    <t>France: May 7, 1956</t>
+  </si>
+  <si>
+    <t>Austrian</t>
+  </si>
+  <si>
+    <t>Dolby Digital</t>
+  </si>
+  <si>
+    <t>French</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1424,14 +1556,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1459,7 +1583,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1900,7 +2024,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -2515,9 +2639,6 @@
       <c r="K11" t="s">
         <v>101</v>
       </c>
-      <c r="L11" t="s">
-        <v>1</v>
-      </c>
       <c r="M11" t="s">
         <v>102</v>
       </c>
@@ -2831,34 +2952,34 @@
         <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="I17" t="s">
         <v>141</v>
       </c>
       <c r="J17" t="s">
-        <v>1</v>
+        <v>481</v>
       </c>
       <c r="K17" t="s">
-        <v>1</v>
+        <v>485</v>
       </c>
       <c r="L17" t="s">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="M17" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="N17" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="O17" t="s">
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>1</v>
+        <v>480</v>
       </c>
       <c r="Q17" t="s">
         <v>1</v>
@@ -3472,6 +3593,9 @@
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>461</v>
+      </c>
       <c r="B38" t="s">
         <v>438</v>
       </c>
@@ -3501,20 +3625,64 @@
       </c>
       <c r="P38" t="s">
         <v>419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>479</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39">
+        <v>1997</v>
+      </c>
+      <c r="E39" t="s">
+        <v>462</v>
+      </c>
+      <c r="F39" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s">
+        <v>503</v>
+      </c>
+      <c r="I39" t="s">
+        <v>463</v>
+      </c>
+      <c r="J39" t="s">
+        <v>469</v>
+      </c>
+      <c r="K39" t="s">
+        <v>470</v>
+      </c>
+      <c r="L39" t="s">
+        <v>471</v>
+      </c>
+      <c r="M39" t="s">
+        <v>94</v>
+      </c>
+      <c r="N39" t="s">
+        <v>472</v>
+      </c>
+      <c r="P39" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R12 A15:R20 A13:F13 H13 L13:N13 P13:R13 A14:D14 F14:H14 K14:O14 Q14:R14" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R10 A15:R16 A13:F13 H13 L13:N13 P13:R13 A14:D14 F14:H14 K14:O14 Q14:R14 A18:R20 A17:F17 O17 I17 Q17:R17 A12:R12 A11:K11 M11:R11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
@@ -4960,8 +5128,133 @@
         <v>387</v>
       </c>
     </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>489</v>
+      </c>
+      <c r="B56" t="s">
+        <v>463</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56">
+        <v>1943</v>
+      </c>
+      <c r="G56" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>490</v>
+      </c>
+      <c r="B57" t="s">
+        <v>464</v>
+      </c>
+      <c r="D57" t="s">
+        <v>484</v>
+      </c>
+      <c r="E57">
+        <v>1912</v>
+      </c>
+      <c r="F57">
+        <v>2006</v>
+      </c>
+      <c r="G57" t="s">
+        <v>502</v>
+      </c>
+    </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D58" s="1"/>
+      <c r="A58" t="s">
+        <v>491</v>
+      </c>
+      <c r="B58" t="s">
+        <v>465</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>492</v>
+      </c>
+      <c r="B59" t="s">
+        <v>466</v>
+      </c>
+      <c r="D59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>493</v>
+      </c>
+      <c r="B60" t="s">
+        <v>467</v>
+      </c>
+      <c r="D60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>494</v>
+      </c>
+      <c r="B61" t="s">
+        <v>468</v>
+      </c>
+      <c r="D61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>495</v>
+      </c>
+      <c r="B62" t="s">
+        <v>482</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>496</v>
+      </c>
+      <c r="B63" t="s">
+        <v>483</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>497</v>
+      </c>
+      <c r="B64" t="s">
+        <v>487</v>
+      </c>
+      <c r="D64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>498</v>
+      </c>
+      <c r="B65" t="s">
+        <v>486</v>
+      </c>
+      <c r="D65" t="s">
+        <v>488</v>
+      </c>
+      <c r="G65" t="s">
+        <v>499</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4974,7 +5267,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -5378,6 +5671,9 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>474</v>
+      </c>
       <c r="B18" t="s">
         <v>419</v>
       </c>
@@ -5389,30 +5685,71 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>475</v>
+      </c>
       <c r="B19" t="s">
         <v>422</v>
       </c>
       <c r="C19" t="s">
         <v>421</v>
       </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>476</v>
+      </c>
       <c r="B20" t="s">
         <v>435</v>
       </c>
       <c r="C20" t="s">
         <v>436</v>
       </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>477</v>
+      </c>
       <c r="B21" t="s">
         <v>445</v>
       </c>
       <c r="C21" t="s">
         <v>446</v>
       </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>478</v>
+      </c>
+      <c r="B22" t="s">
+        <v>473</v>
+      </c>
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>500</v>
+      </c>
+      <c r="B23" t="s">
+        <v>480</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:G2 A4:G17 A3:B3 E3:G3" numberStoredAsText="1"/>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07206204-A025-6F49-AEB9-6731F307C395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D773D705-B7C8-7C43-BD6B-B5EFC422171B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-7260" windowWidth="38400" windowHeight="12740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-8880" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="569">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1173,12 +1173,6 @@
     <t>Spring Comes to Lhasa</t>
   </si>
   <si>
-    <t>春到西藏</t>
-  </si>
-  <si>
-    <t>Spring Comes to Tibet</t>
-  </si>
-  <si>
     <t>民族万岁</t>
   </si>
   <si>
@@ -1491,9 +1485,6 @@
     <t>Peter Aufschnaiter</t>
   </si>
   <si>
-    <t>Casr</t>
-  </si>
-  <si>
     <t>PERSON-0055</t>
   </si>
   <si>
@@ -1540,6 +1531,207 @@
   </si>
   <si>
     <t>French</t>
+  </si>
+  <si>
+    <t>丫丫</t>
+  </si>
+  <si>
+    <t>雪山泪</t>
+  </si>
+  <si>
+    <t>女活佛</t>
+  </si>
+  <si>
+    <t>卓瓦桑姆</t>
+  </si>
+  <si>
+    <t>松赞干布</t>
+  </si>
+  <si>
+    <t>世界屋脊上的太阳</t>
+  </si>
+  <si>
+    <t>布达拉宫秘史</t>
+  </si>
+  <si>
+    <t>红河谷</t>
+  </si>
+  <si>
+    <t>弹起我的扎年琴</t>
+  </si>
+  <si>
+    <t>FILM-0039</t>
+  </si>
+  <si>
+    <t>FILM-0040</t>
+  </si>
+  <si>
+    <t>FILM-0041</t>
+  </si>
+  <si>
+    <t>FILM-0042</t>
+  </si>
+  <si>
+    <t>FILM-0043</t>
+  </si>
+  <si>
+    <t>FILM-0044</t>
+  </si>
+  <si>
+    <t>FILM-0045</t>
+  </si>
+  <si>
+    <t>FILM-0046</t>
+  </si>
+  <si>
+    <t>111 min</t>
+  </si>
+  <si>
+    <t>Ya Ya</t>
+  </si>
+  <si>
+    <t>China: March, 1979</t>
+  </si>
+  <si>
+    <t>Sun Yu</t>
+  </si>
+  <si>
+    <t>Liu Ke</t>
+  </si>
+  <si>
+    <t>孙羽</t>
+  </si>
+  <si>
+    <t>刘克</t>
+  </si>
+  <si>
+    <t>Song Xiaoying</t>
+  </si>
+  <si>
+    <t>Bai Zhen</t>
+  </si>
+  <si>
+    <t>素南绕登</t>
+  </si>
+  <si>
+    <t>宋晓英</t>
+  </si>
+  <si>
+    <t>白珍</t>
+  </si>
+  <si>
+    <t>Changchun Film Studio</t>
+  </si>
+  <si>
+    <t>长春电影制片厂</t>
+  </si>
+  <si>
+    <t>Forbidden to be Born</t>
+  </si>
+  <si>
+    <t>104 min</t>
+  </si>
+  <si>
+    <t>Hua Chun;Ren Pengyuan</t>
+  </si>
+  <si>
+    <t>Hua Chun</t>
+  </si>
+  <si>
+    <t>Ren Pengyuan</t>
+  </si>
+  <si>
+    <t>Wang Ying</t>
+  </si>
+  <si>
+    <t>Wangdui</t>
+  </si>
+  <si>
+    <t>Zhaxi Lamu</t>
+  </si>
+  <si>
+    <t>Baima Yangjie</t>
+  </si>
+  <si>
+    <t>Laba Dunzhu</t>
+  </si>
+  <si>
+    <t>Yangjinzhuoga</t>
+  </si>
+  <si>
+    <t>Sunanraodeng</t>
+  </si>
+  <si>
+    <t>华纯</t>
+  </si>
+  <si>
+    <t>任鹏远</t>
+  </si>
+  <si>
+    <t>旺堆</t>
+  </si>
+  <si>
+    <t>扎西拉姆</t>
+  </si>
+  <si>
+    <t>白玛央杰</t>
+  </si>
+  <si>
+    <t>拉巴顿珠</t>
+  </si>
+  <si>
+    <t>王颖</t>
+  </si>
+  <si>
+    <t>央金卓嘎</t>
+  </si>
+  <si>
+    <t>Song Xiaoying;Bai Zhen;Sunanraodeng</t>
+  </si>
+  <si>
+    <t>Wangdui;Zhaxilamu;Baimayangjie;Labadunzhu;Yangjinzhuoga</t>
+  </si>
+  <si>
+    <t>PERSON-0066</t>
+  </si>
+  <si>
+    <t>PERSON-0067</t>
+  </si>
+  <si>
+    <t>PERSON-0068</t>
+  </si>
+  <si>
+    <t>PERSON-0069</t>
+  </si>
+  <si>
+    <t>PERSON-0070</t>
+  </si>
+  <si>
+    <t>PERSON-0071</t>
+  </si>
+  <si>
+    <t>PERSON-0072</t>
+  </si>
+  <si>
+    <t>PERSON-0073</t>
+  </si>
+  <si>
+    <t>PERSON-0074</t>
+  </si>
+  <si>
+    <t>PERSON-0075</t>
+  </si>
+  <si>
+    <t>PERSON-0076</t>
+  </si>
+  <si>
+    <t>PERSON-0077</t>
+  </si>
+  <si>
+    <t>PERSON-0078</t>
+  </si>
+  <si>
+    <t>ORG-0023</t>
   </si>
 </sst>
 </file>
@@ -1581,9 +1773,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2024,7 +2215,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -2778,7 +2969,7 @@
         <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F14" t="s">
         <v>51</v>
@@ -2790,10 +2981,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J14" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K14" t="s">
         <v>1</v>
@@ -2811,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q14" t="s">
         <v>1</v>
@@ -2961,13 +3152,13 @@
         <v>141</v>
       </c>
       <c r="J17" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="K17" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L17" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="M17" t="s">
         <v>53</v>
@@ -2979,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Q17" t="s">
         <v>1</v>
@@ -3190,7 +3381,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B22" t="s">
         <v>364</v>
@@ -3205,7 +3396,7 @@
         <v>51</v>
       </c>
       <c r="I22" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M22" t="s">
         <v>365</v>
@@ -3213,7 +3404,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B23" t="s">
         <v>366</v>
@@ -3236,7 +3427,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B24" t="s">
         <v>369</v>
@@ -3259,7 +3450,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B25" t="s">
         <v>371</v>
@@ -3282,7 +3473,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B26" t="s">
         <v>372</v>
@@ -3297,10 +3488,10 @@
         <v>51</v>
       </c>
       <c r="I26" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J26" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M26" t="s">
         <v>79</v>
@@ -3309,12 +3500,12 @@
         <v>123</v>
       </c>
       <c r="P26" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B27" t="s">
         <v>375</v>
@@ -3326,16 +3517,16 @@
         <v>1963</v>
       </c>
       <c r="E27" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F27" t="s">
         <v>38</v>
       </c>
       <c r="I27" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J27" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M27" t="s">
         <v>79</v>
@@ -3344,12 +3535,12 @@
         <v>123</v>
       </c>
       <c r="P27" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B28" t="s">
         <v>378</v>
@@ -3369,7 +3560,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B29" t="s">
         <v>379</v>
@@ -3392,7 +3583,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B30" t="s">
         <v>381</v>
@@ -3412,16 +3603,31 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B31" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C31" t="s">
         <v>382</v>
       </c>
       <c r="D31">
-        <v>1956</v>
+        <v>1939</v>
+      </c>
+      <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" t="s">
+        <v>383</v>
+      </c>
+      <c r="L31" t="s">
+        <v>386</v>
       </c>
       <c r="M31" t="s">
         <v>79</v>
@@ -3432,31 +3638,16 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B32" t="s">
+        <v>388</v>
+      </c>
+      <c r="C32" t="s">
         <v>389</v>
       </c>
-      <c r="C32" t="s">
-        <v>384</v>
-      </c>
       <c r="D32">
-        <v>1939</v>
-      </c>
-      <c r="E32" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" t="s">
-        <v>39</v>
-      </c>
-      <c r="I32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L32" t="s">
-        <v>388</v>
+        <v>1958</v>
       </c>
       <c r="M32" t="s">
         <v>79</v>
@@ -3467,16 +3658,16 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B33" t="s">
+        <v>391</v>
+      </c>
+      <c r="C33" t="s">
         <v>390</v>
       </c>
-      <c r="C33" t="s">
-        <v>391</v>
-      </c>
       <c r="D33">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="M33" t="s">
         <v>79</v>
@@ -3487,16 +3678,25 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B34" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" t="s">
         <v>393</v>
       </c>
-      <c r="C34" t="s">
-        <v>392</v>
-      </c>
       <c r="D34">
-        <v>1959</v>
+        <v>1961</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" t="s">
+        <v>441</v>
+      </c>
+      <c r="J34" t="s">
+        <v>442</v>
       </c>
       <c r="M34" t="s">
         <v>79</v>
@@ -3504,42 +3704,36 @@
       <c r="N34" t="s">
         <v>123</v>
       </c>
+      <c r="P34" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B35" t="s">
+        <v>395</v>
+      </c>
+      <c r="C35" t="s">
         <v>394</v>
       </c>
-      <c r="C35" t="s">
-        <v>395</v>
-      </c>
       <c r="D35">
-        <v>1961</v>
+        <v>1953</v>
       </c>
       <c r="F35" t="s">
         <v>51</v>
       </c>
-      <c r="I35" t="s">
-        <v>443</v>
-      </c>
-      <c r="J35" t="s">
-        <v>444</v>
-      </c>
       <c r="M35" t="s">
         <v>79</v>
       </c>
       <c r="N35" t="s">
         <v>123</v>
       </c>
-      <c r="P35" t="s">
-        <v>445</v>
-      </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B36" t="s">
         <v>397</v>
@@ -3548,38 +3742,50 @@
         <v>396</v>
       </c>
       <c r="D36">
-        <v>1953</v>
+        <v>1956</v>
+      </c>
+      <c r="E36" t="s">
+        <v>427</v>
       </c>
       <c r="F36" t="s">
         <v>51</v>
       </c>
+      <c r="I36" t="s">
+        <v>428</v>
+      </c>
       <c r="M36" t="s">
         <v>79</v>
       </c>
       <c r="N36" t="s">
         <v>123</v>
       </c>
+      <c r="P36" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B37" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="C37" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
       <c r="D37">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="E37" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="I37" t="s">
+        <v>439</v>
+      </c>
+      <c r="J37" t="s">
         <v>430</v>
       </c>
       <c r="M37" t="s">
@@ -3589,56 +3795,68 @@
         <v>123</v>
       </c>
       <c r="P37" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B38" t="s">
-        <v>438</v>
-      </c>
-      <c r="C38" t="s">
-        <v>439</v>
+        <v>138</v>
       </c>
       <c r="D38">
-        <v>1955</v>
+        <v>1997</v>
       </c>
       <c r="E38" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="F38" t="s">
         <v>38</v>
       </c>
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" t="s">
+        <v>500</v>
+      </c>
       <c r="I38" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="J38" t="s">
-        <v>432</v>
+        <v>467</v>
+      </c>
+      <c r="K38" t="s">
+        <v>468</v>
+      </c>
+      <c r="L38" t="s">
+        <v>469</v>
       </c>
       <c r="M38" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="N38" t="s">
-        <v>123</v>
+        <v>470</v>
       </c>
       <c r="P38" t="s">
-        <v>419</v>
+        <v>471</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>533</v>
+      </c>
+      <c r="C39" t="s">
+        <v>503</v>
       </c>
       <c r="D39">
-        <v>1997</v>
+        <v>1979</v>
       </c>
       <c r="E39" t="s">
-        <v>462</v>
+        <v>534</v>
       </c>
       <c r="F39" t="s">
         <v>38</v>
@@ -3646,29 +3864,186 @@
       <c r="G39" t="s">
         <v>21</v>
       </c>
-      <c r="H39" t="s">
-        <v>503</v>
-      </c>
       <c r="I39" t="s">
-        <v>463</v>
+        <v>535</v>
       </c>
       <c r="J39" t="s">
-        <v>469</v>
+        <v>538</v>
       </c>
       <c r="K39" t="s">
-        <v>470</v>
-      </c>
-      <c r="L39" t="s">
-        <v>471</v>
+        <v>554</v>
       </c>
       <c r="M39" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="N39" t="s">
-        <v>472</v>
+        <v>123</v>
       </c>
       <c r="P39" t="s">
-        <v>473</v>
+        <v>433</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>511</v>
+      </c>
+      <c r="C40" t="s">
+        <v>504</v>
+      </c>
+      <c r="F40" t="s">
+        <v>38</v>
+      </c>
+      <c r="M40" t="s">
+        <v>79</v>
+      </c>
+      <c r="N40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>512</v>
+      </c>
+      <c r="C41" t="s">
+        <v>505</v>
+      </c>
+      <c r="F41" t="s">
+        <v>38</v>
+      </c>
+      <c r="M41" t="s">
+        <v>79</v>
+      </c>
+      <c r="N41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>513</v>
+      </c>
+      <c r="C42" t="s">
+        <v>506</v>
+      </c>
+      <c r="F42" t="s">
+        <v>38</v>
+      </c>
+      <c r="M42" t="s">
+        <v>79</v>
+      </c>
+      <c r="N42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>514</v>
+      </c>
+      <c r="C43" t="s">
+        <v>507</v>
+      </c>
+      <c r="F43" t="s">
+        <v>38</v>
+      </c>
+      <c r="M43" t="s">
+        <v>79</v>
+      </c>
+      <c r="N43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>515</v>
+      </c>
+      <c r="C44" t="s">
+        <v>508</v>
+      </c>
+      <c r="F44" t="s">
+        <v>38</v>
+      </c>
+      <c r="M44" t="s">
+        <v>79</v>
+      </c>
+      <c r="N44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>516</v>
+      </c>
+      <c r="C45" t="s">
+        <v>509</v>
+      </c>
+      <c r="F45" t="s">
+        <v>38</v>
+      </c>
+      <c r="M45" t="s">
+        <v>79</v>
+      </c>
+      <c r="N45" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>517</v>
+      </c>
+      <c r="C46" t="s">
+        <v>510</v>
+      </c>
+      <c r="F46" t="s">
+        <v>38</v>
+      </c>
+      <c r="M46" t="s">
+        <v>79</v>
+      </c>
+      <c r="N46" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>518</v>
+      </c>
+      <c r="B47" t="s">
+        <v>520</v>
+      </c>
+      <c r="C47" t="s">
+        <v>502</v>
+      </c>
+      <c r="D47">
+        <v>1979</v>
+      </c>
+      <c r="E47" t="s">
+        <v>519</v>
+      </c>
+      <c r="F47" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s">
+        <v>522</v>
+      </c>
+      <c r="J47" t="s">
+        <v>523</v>
+      </c>
+      <c r="K47" t="s">
+        <v>553</v>
+      </c>
+      <c r="L47" t="s">
+        <v>521</v>
+      </c>
+      <c r="M47" t="s">
+        <v>79</v>
+      </c>
+      <c r="N47" t="s">
+        <v>123</v>
+      </c>
+      <c r="P47" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -3682,7 +4057,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
@@ -4966,95 +5341,95 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B46" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C46" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D46" t="s">
         <v>23</v>
       </c>
       <c r="G46" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D47" t="s">
         <v>194</v>
       </c>
       <c r="G47" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C48" t="s">
         <v>425</v>
-      </c>
-      <c r="C48" t="s">
-        <v>427</v>
       </c>
       <c r="D48" t="s">
         <v>194</v>
       </c>
       <c r="G48" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B49" t="s">
+        <v>424</v>
+      </c>
+      <c r="C49" t="s">
         <v>426</v>
-      </c>
-      <c r="C49" t="s">
-        <v>428</v>
       </c>
       <c r="D49" t="s">
         <v>194</v>
       </c>
       <c r="G49" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s">
+        <v>430</v>
+      </c>
+      <c r="C50" t="s">
         <v>432</v>
-      </c>
-      <c r="C50" t="s">
-        <v>434</v>
       </c>
       <c r="D50" t="s">
         <v>194</v>
       </c>
       <c r="G50" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D51" t="s">
         <v>23</v>
@@ -5062,78 +5437,78 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C52" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D52" t="s">
         <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C53" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B54" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C54" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
       </c>
       <c r="G54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B55" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C55" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D55" t="s">
         <v>23</v>
       </c>
       <c r="G55" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D56" t="s">
         <v>23</v>
@@ -5142,18 +5517,18 @@
         <v>1943</v>
       </c>
       <c r="G56" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D57" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E57">
         <v>1912</v>
@@ -5162,26 +5537,26 @@
         <v>2006</v>
       </c>
       <c r="G57" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s">
-        <v>465</v>
-      </c>
-      <c r="D58" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D58" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D59" t="s">
         <v>25</v>
@@ -5189,10 +5564,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D60" t="s">
         <v>25</v>
@@ -5200,10 +5575,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D61" t="s">
         <v>25</v>
@@ -5211,10 +5586,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B62" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
@@ -5222,10 +5597,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B63" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -5233,10 +5608,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B64" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D64" t="s">
         <v>25</v>
@@ -5244,16 +5619,198 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D65" t="s">
-        <v>488</v>
+        <v>25</v>
       </c>
       <c r="G65" t="s">
-        <v>499</v>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>555</v>
+      </c>
+      <c r="B66" t="s">
+        <v>522</v>
+      </c>
+      <c r="C66" t="s">
+        <v>524</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>556</v>
+      </c>
+      <c r="B67" t="s">
+        <v>523</v>
+      </c>
+      <c r="C67" t="s">
+        <v>525</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>557</v>
+      </c>
+      <c r="B68" t="s">
+        <v>526</v>
+      </c>
+      <c r="C68" t="s">
+        <v>529</v>
+      </c>
+      <c r="D68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>558</v>
+      </c>
+      <c r="B69" t="s">
+        <v>527</v>
+      </c>
+      <c r="C69" t="s">
+        <v>530</v>
+      </c>
+      <c r="D69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>559</v>
+      </c>
+      <c r="B70" t="s">
+        <v>544</v>
+      </c>
+      <c r="C70" t="s">
+        <v>528</v>
+      </c>
+      <c r="D70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>560</v>
+      </c>
+      <c r="B71" t="s">
+        <v>536</v>
+      </c>
+      <c r="C71" t="s">
+        <v>545</v>
+      </c>
+      <c r="D71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>561</v>
+      </c>
+      <c r="B72" t="s">
+        <v>537</v>
+      </c>
+      <c r="C72" t="s">
+        <v>546</v>
+      </c>
+      <c r="D72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>562</v>
+      </c>
+      <c r="B73" t="s">
+        <v>538</v>
+      </c>
+      <c r="C73" t="s">
+        <v>551</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>563</v>
+      </c>
+      <c r="B74" t="s">
+        <v>539</v>
+      </c>
+      <c r="C74" t="s">
+        <v>547</v>
+      </c>
+      <c r="D74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>564</v>
+      </c>
+      <c r="B75" t="s">
+        <v>540</v>
+      </c>
+      <c r="C75" t="s">
+        <v>548</v>
+      </c>
+      <c r="D75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>565</v>
+      </c>
+      <c r="B76" t="s">
+        <v>541</v>
+      </c>
+      <c r="C76" t="s">
+        <v>549</v>
+      </c>
+      <c r="D76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>566</v>
+      </c>
+      <c r="B77" t="s">
+        <v>542</v>
+      </c>
+      <c r="C77" t="s">
+        <v>550</v>
+      </c>
+      <c r="D77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>567</v>
+      </c>
+      <c r="B78" t="s">
+        <v>543</v>
+      </c>
+      <c r="C78" t="s">
+        <v>552</v>
+      </c>
+      <c r="D78" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -5267,7 +5824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -5333,7 +5890,7 @@
         <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D3" t="s">
         <v>79</v>
@@ -5672,13 +6229,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B18" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -5686,13 +6243,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C19" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -5700,13 +6257,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B20" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C20" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -5714,13 +6271,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B21" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C21" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -5728,10 +6285,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B22" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D22" t="s">
         <v>94</v>
@@ -5742,10 +6299,27 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B23" t="s">
-        <v>480</v>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>568</v>
+      </c>
+      <c r="B24" t="s">
+        <v>531</v>
+      </c>
+      <c r="C24" t="s">
+        <v>532</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24">
+        <v>1945</v>
       </c>
     </row>
   </sheetData>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D773D705-B7C8-7C43-BD6B-B5EFC422171B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5884DB-E312-A24E-A408-2D49DA4C50A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-8880" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="697">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1473,9 +1473,6 @@
     <t>George Campey</t>
   </si>
   <si>
-    <t>Writer;Cast</t>
-  </si>
-  <si>
     <t>Heinrich Harrer;Peter Aufschnaiter;The Dalai Lama</t>
   </si>
   <si>
@@ -1647,15 +1644,6 @@
     <t>Wangdui</t>
   </si>
   <si>
-    <t>Zhaxi Lamu</t>
-  </si>
-  <si>
-    <t>Baima Yangjie</t>
-  </si>
-  <si>
-    <t>Laba Dunzhu</t>
-  </si>
-  <si>
     <t>Yangjinzhuoga</t>
   </si>
   <si>
@@ -1732,6 +1720,402 @@
   </si>
   <si>
     <t>ORG-0023</t>
+  </si>
+  <si>
+    <t>143 min</t>
+  </si>
+  <si>
+    <t>Li Wei</t>
+  </si>
+  <si>
+    <t>Qin Wenyu</t>
+  </si>
+  <si>
+    <t>Pubuzhuoma;Zhaxidunzhu;Zhuoma;Luosangjiayang;Duojie</t>
+  </si>
+  <si>
+    <t>Pubuzhuoma</t>
+  </si>
+  <si>
+    <t>Zhaxidunzhu</t>
+  </si>
+  <si>
+    <t>Labadunzhu</t>
+  </si>
+  <si>
+    <t>Zhaxilamu</t>
+  </si>
+  <si>
+    <t>Baimayangjie</t>
+  </si>
+  <si>
+    <t>Zhuoma</t>
+  </si>
+  <si>
+    <t>Luosangjiayang</t>
+  </si>
+  <si>
+    <t>Duoji</t>
+  </si>
+  <si>
+    <t>李伟</t>
+  </si>
+  <si>
+    <t>秦文玉</t>
+  </si>
+  <si>
+    <t>卓玛</t>
+  </si>
+  <si>
+    <t>洛桑加央</t>
+  </si>
+  <si>
+    <t>普布卓玛</t>
+  </si>
+  <si>
+    <t>扎西顿珠</t>
+  </si>
+  <si>
+    <t>多吉</t>
+  </si>
+  <si>
+    <t>Zhang Yi</t>
+  </si>
+  <si>
+    <t>Huang Zhilong</t>
+  </si>
+  <si>
+    <t>Mandarin;Tibetan</t>
+  </si>
+  <si>
+    <t>Tibet Film Dubbing Studio</t>
+  </si>
+  <si>
+    <t>西藏电影译制片厂</t>
+  </si>
+  <si>
+    <t>Emei Film Studio</t>
+  </si>
+  <si>
+    <t>峨眉电影制片厂</t>
+  </si>
+  <si>
+    <t>Tibet Film Dubbing Studio;Emei Film Studio</t>
+  </si>
+  <si>
+    <t>Luodan</t>
+  </si>
+  <si>
+    <t>Duobujie</t>
+  </si>
+  <si>
+    <t>张一</t>
+  </si>
+  <si>
+    <t>黄志龙</t>
+  </si>
+  <si>
+    <t>洛桑群培</t>
+  </si>
+  <si>
+    <t>洛丹</t>
+  </si>
+  <si>
+    <t>多布杰</t>
+  </si>
+  <si>
+    <t>Feirt Zhouwa Sangmu</t>
+  </si>
+  <si>
+    <t>Zhaxidunzhu;Losang Choepel;Duoji;Luodan;Duobujie</t>
+  </si>
+  <si>
+    <t>Losang Choepel</t>
+  </si>
+  <si>
+    <t>Snow Leopard</t>
+  </si>
+  <si>
+    <t>109 min</t>
+  </si>
+  <si>
+    <t>Pema Tseden</t>
+  </si>
+  <si>
+    <t>Jinpa;Tseten Tashi;Lobsang Choepel</t>
+  </si>
+  <si>
+    <t>万玛才旦</t>
+  </si>
+  <si>
+    <t>jinpa</t>
+  </si>
+  <si>
+    <t>Tseten Tashi</t>
+  </si>
+  <si>
+    <t>Writer;Actor</t>
+  </si>
+  <si>
+    <t>China: April 3, 2024</t>
+  </si>
+  <si>
+    <t>Beijing Nanji Pictures</t>
+  </si>
+  <si>
+    <t>北京南吉影业有限公司</t>
+  </si>
+  <si>
+    <t>中国电影股份有限公司</t>
+  </si>
+  <si>
+    <t>China Film Co., Ltd.</t>
+  </si>
+  <si>
+    <t>China Film Co., Ltd.;Beijing Nanji Pictures</t>
+  </si>
+  <si>
+    <t>Jia Mu</t>
+  </si>
+  <si>
+    <t>Chong Hua</t>
+  </si>
+  <si>
+    <t>Zhang Ping;Danzhouduoji;Liang Xiaorong;Awangkecun</t>
+  </si>
+  <si>
+    <t>Zhang Ping</t>
+  </si>
+  <si>
+    <t>Danzhouduoji</t>
+  </si>
+  <si>
+    <t>Liang Xiaorong</t>
+  </si>
+  <si>
+    <t>Awangkecun</t>
+  </si>
+  <si>
+    <t>阿旺克村</t>
+  </si>
+  <si>
+    <t>梁晓蓉</t>
+  </si>
+  <si>
+    <t>旦周多吉</t>
+  </si>
+  <si>
+    <t>张平</t>
+  </si>
+  <si>
+    <t>重华</t>
+  </si>
+  <si>
+    <t>佳木</t>
+  </si>
+  <si>
+    <t>成都市歌舞剧团</t>
+  </si>
+  <si>
+    <t>Chengdu Song and Dance Troupe</t>
+  </si>
+  <si>
+    <t>Spring Comes to Tibet</t>
+  </si>
+  <si>
+    <t>春到西藏</t>
+  </si>
+  <si>
+    <t>The Female Living Buddha</t>
+  </si>
+  <si>
+    <t>86 min</t>
+  </si>
+  <si>
+    <t>The King Songtsan Ganbu</t>
+  </si>
+  <si>
+    <t>杨吉爻</t>
+  </si>
+  <si>
+    <t>Yang Jiyao</t>
+  </si>
+  <si>
+    <t>Pubuciren</t>
+  </si>
+  <si>
+    <t>Luosangciren</t>
+  </si>
+  <si>
+    <t>Danzeng</t>
+  </si>
+  <si>
+    <t>Li Yang</t>
+  </si>
+  <si>
+    <t>Mingmacaidan</t>
+  </si>
+  <si>
+    <t>Puzhen</t>
+  </si>
+  <si>
+    <t>Dunzhuduoji</t>
+  </si>
+  <si>
+    <t>顿珠多吉</t>
+  </si>
+  <si>
+    <t>普珍</t>
+  </si>
+  <si>
+    <t>明玛才仁</t>
+  </si>
+  <si>
+    <t>李阳</t>
+  </si>
+  <si>
+    <t>旦增</t>
+  </si>
+  <si>
+    <t>洛桑次仁</t>
+  </si>
+  <si>
+    <t>普布次仁</t>
+  </si>
+  <si>
+    <t>Pubuciren;Yang Jiyao;Luosangciren;Danzeng</t>
+  </si>
+  <si>
+    <t>Li Yang;Mingmacairen</t>
+  </si>
+  <si>
+    <t>Zhaxidunzhu;Losang Choepel;Puzhen;Pubuzhuoma;Dunzhuduoji</t>
+  </si>
+  <si>
+    <t>115 min</t>
+  </si>
+  <si>
+    <t>Red River Valley</t>
+  </si>
+  <si>
+    <t>雪豹;གསའ།</t>
+  </si>
+  <si>
+    <t>Play My Dranyen</t>
+  </si>
+  <si>
+    <t>The Sun over the Roof of the World</t>
+  </si>
+  <si>
+    <t>The Secret History of the Potala Palace</t>
+  </si>
+  <si>
+    <t>FILM-0047</t>
+  </si>
+  <si>
+    <t>FILM-0048</t>
+  </si>
+  <si>
+    <t>PERSON-0079</t>
+  </si>
+  <si>
+    <t>PERSON-0080</t>
+  </si>
+  <si>
+    <t>PERSON-0081</t>
+  </si>
+  <si>
+    <t>PERSON-0082</t>
+  </si>
+  <si>
+    <t>PERSON-0083</t>
+  </si>
+  <si>
+    <t>PERSON-0084</t>
+  </si>
+  <si>
+    <t>PERSON-0085</t>
+  </si>
+  <si>
+    <t>PERSON-0086</t>
+  </si>
+  <si>
+    <t>PERSON-0087</t>
+  </si>
+  <si>
+    <t>PERSON-0088</t>
+  </si>
+  <si>
+    <t>PERSON-0089</t>
+  </si>
+  <si>
+    <t>PERSON-0090</t>
+  </si>
+  <si>
+    <t>PERSON-0091</t>
+  </si>
+  <si>
+    <t>PERSON-0092</t>
+  </si>
+  <si>
+    <t>PERSON-0093</t>
+  </si>
+  <si>
+    <t>PERSON-0094</t>
+  </si>
+  <si>
+    <t>PERSON-0095</t>
+  </si>
+  <si>
+    <t>PERSON-0096</t>
+  </si>
+  <si>
+    <t>PERSON-0097</t>
+  </si>
+  <si>
+    <t>PERSON-0098</t>
+  </si>
+  <si>
+    <t>PERSON-0099</t>
+  </si>
+  <si>
+    <t>PERSON-0100</t>
+  </si>
+  <si>
+    <t>PERSON-0101</t>
+  </si>
+  <si>
+    <t>PERSON-0102</t>
+  </si>
+  <si>
+    <t>PERSON-0103</t>
+  </si>
+  <si>
+    <t>PERSON-0104</t>
+  </si>
+  <si>
+    <t>PERSON-0105</t>
+  </si>
+  <si>
+    <t>PERSON-0106</t>
+  </si>
+  <si>
+    <t>PERSON-0107</t>
+  </si>
+  <si>
+    <t>ORG-0024</t>
+  </si>
+  <si>
+    <t>ORG-0025</t>
+  </si>
+  <si>
+    <t>ORG-0026</t>
+  </si>
+  <si>
+    <t>ORG-0027</t>
+  </si>
+  <si>
+    <t>ORG-0028</t>
   </si>
 </sst>
 </file>
@@ -2215,7 +2599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -3155,10 +3539,10 @@
         <v>479</v>
       </c>
       <c r="K17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="M17" t="s">
         <v>53</v>
@@ -3818,7 +4202,7 @@
         <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I38" t="s">
         <v>461</v>
@@ -3847,16 +4231,16 @@
         <v>477</v>
       </c>
       <c r="B39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C39" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D39">
         <v>1979</v>
       </c>
       <c r="E39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F39" t="s">
         <v>38</v>
@@ -3865,13 +4249,13 @@
         <v>21</v>
       </c>
       <c r="I39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J39" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K39" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="M39" t="s">
         <v>79</v>
@@ -3885,48 +4269,117 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c r="B40" t="s">
+        <v>633</v>
       </c>
       <c r="C40" t="s">
-        <v>504</v>
+        <v>503</v>
+      </c>
+      <c r="D40">
+        <v>1986</v>
+      </c>
+      <c r="E40" t="s">
+        <v>565</v>
       </c>
       <c r="F40" t="s">
         <v>38</v>
       </c>
+      <c r="G40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s">
+        <v>566</v>
+      </c>
+      <c r="J40" t="s">
+        <v>567</v>
+      </c>
+      <c r="K40" t="s">
+        <v>568</v>
+      </c>
       <c r="M40" t="s">
         <v>79</v>
       </c>
       <c r="N40" t="s">
         <v>123</v>
       </c>
+      <c r="P40" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c r="B41" t="s">
+        <v>599</v>
       </c>
       <c r="C41" t="s">
-        <v>505</v>
+        <v>504</v>
+      </c>
+      <c r="D41">
+        <v>1984</v>
+      </c>
+      <c r="E41" t="s">
+        <v>438</v>
       </c>
       <c r="F41" t="s">
         <v>38</v>
       </c>
+      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s">
+        <v>616</v>
+      </c>
+      <c r="J41" t="s">
+        <v>617</v>
+      </c>
+      <c r="K41" t="s">
+        <v>618</v>
+      </c>
       <c r="M41" t="s">
         <v>79</v>
       </c>
       <c r="N41" t="s">
         <v>123</v>
       </c>
+      <c r="P41" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>513</v>
+        <v>512</v>
+      </c>
+      <c r="B42" t="s">
+        <v>635</v>
       </c>
       <c r="C42" t="s">
-        <v>506</v>
+        <v>505</v>
+      </c>
+      <c r="D42">
+        <v>1988</v>
+      </c>
+      <c r="E42" t="s">
+        <v>634</v>
       </c>
       <c r="F42" t="s">
         <v>38</v>
       </c>
+      <c r="G42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s">
+        <v>652</v>
+      </c>
+      <c r="J42" t="s">
+        <v>653</v>
+      </c>
+      <c r="K42" t="s">
+        <v>654</v>
+      </c>
       <c r="M42" t="s">
         <v>79</v>
       </c>
@@ -3936,10 +4389,19 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>514</v>
+        <v>513</v>
+      </c>
+      <c r="B43" t="s">
+        <v>659</v>
       </c>
       <c r="C43" t="s">
-        <v>507</v>
+        <v>506</v>
+      </c>
+      <c r="D43">
+        <v>1990</v>
+      </c>
+      <c r="E43" t="s">
+        <v>127</v>
       </c>
       <c r="F43" t="s">
         <v>38</v>
@@ -3953,27 +4415,57 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>515</v>
+        <v>514</v>
+      </c>
+      <c r="B44" t="s">
+        <v>660</v>
       </c>
       <c r="C44" t="s">
-        <v>508</v>
+        <v>507</v>
+      </c>
+      <c r="D44">
+        <v>1989</v>
       </c>
       <c r="F44" t="s">
         <v>38</v>
       </c>
+      <c r="G44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s">
+        <v>584</v>
+      </c>
+      <c r="J44" t="s">
+        <v>585</v>
+      </c>
+      <c r="K44" t="s">
+        <v>600</v>
+      </c>
       <c r="M44" t="s">
         <v>79</v>
       </c>
       <c r="N44" t="s">
-        <v>123</v>
+        <v>586</v>
+      </c>
+      <c r="P44" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>516</v>
+        <v>515</v>
+      </c>
+      <c r="B45" t="s">
+        <v>656</v>
       </c>
       <c r="C45" t="s">
-        <v>509</v>
+        <v>508</v>
+      </c>
+      <c r="D45">
+        <v>1996</v>
+      </c>
+      <c r="E45" t="s">
+        <v>655</v>
       </c>
       <c r="F45" t="s">
         <v>38</v>
@@ -3987,10 +4479,19 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>517</v>
+        <v>516</v>
+      </c>
+      <c r="B46" t="s">
+        <v>658</v>
       </c>
       <c r="C46" t="s">
-        <v>510</v>
+        <v>509</v>
+      </c>
+      <c r="D46">
+        <v>1999</v>
+      </c>
+      <c r="E46" t="s">
+        <v>351</v>
       </c>
       <c r="F46" t="s">
         <v>38</v>
@@ -4004,19 +4505,19 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B47" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C47" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D47">
         <v>1979</v>
       </c>
       <c r="E47" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F47" t="s">
         <v>38</v>
@@ -4025,16 +4526,16 @@
         <v>21</v>
       </c>
       <c r="I47" t="s">
+        <v>521</v>
+      </c>
+      <c r="J47" t="s">
         <v>522</v>
       </c>
-      <c r="J47" t="s">
-        <v>523</v>
-      </c>
       <c r="K47" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="L47" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M47" t="s">
         <v>79</v>
@@ -4043,7 +4544,74 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>531</v>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>661</v>
+      </c>
+      <c r="B48" t="s">
+        <v>602</v>
+      </c>
+      <c r="C48" t="s">
+        <v>657</v>
+      </c>
+      <c r="D48">
+        <v>2023</v>
+      </c>
+      <c r="E48" t="s">
+        <v>603</v>
+      </c>
+      <c r="F48" t="s">
+        <v>38</v>
+      </c>
+      <c r="G48" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s">
+        <v>604</v>
+      </c>
+      <c r="J48" t="s">
+        <v>604</v>
+      </c>
+      <c r="K48" t="s">
+        <v>605</v>
+      </c>
+      <c r="L48" t="s">
+        <v>610</v>
+      </c>
+      <c r="M48" t="s">
+        <v>79</v>
+      </c>
+      <c r="N48" t="s">
+        <v>586</v>
+      </c>
+      <c r="P48" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>662</v>
+      </c>
+      <c r="B49" t="s">
+        <v>631</v>
+      </c>
+      <c r="C49" t="s">
+        <v>632</v>
+      </c>
+      <c r="D49">
+        <v>1956</v>
+      </c>
+      <c r="M49" t="s">
+        <v>79</v>
+      </c>
+      <c r="N49" t="s">
+        <v>123</v>
+      </c>
+      <c r="P49" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -4057,7 +4625,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
@@ -5307,7 +5875,7 @@
         <v>358</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="E44">
         <v>1903</v>
@@ -5327,7 +5895,7 @@
         <v>359</v>
       </c>
       <c r="D45" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="E45">
         <v>1908</v>
@@ -5505,7 +6073,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s">
         <v>461</v>
@@ -5517,18 +6085,18 @@
         <v>1943</v>
       </c>
       <c r="G56" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s">
         <v>462</v>
       </c>
       <c r="D57" t="s">
-        <v>482</v>
+        <v>609</v>
       </c>
       <c r="E57">
         <v>1912</v>
@@ -5537,12 +6105,12 @@
         <v>2006</v>
       </c>
       <c r="G57" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s">
         <v>463</v>
@@ -5553,40 +6121,40 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s">
         <v>464</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s">
         <v>465</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s">
         <v>466</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s">
         <v>480</v>
@@ -5597,7 +6165,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B63" t="s">
         <v>481</v>
@@ -5608,38 +6176,38 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>494</v>
+      </c>
+      <c r="B65" t="s">
+        <v>483</v>
+      </c>
+      <c r="D65" t="s">
+        <v>190</v>
+      </c>
+      <c r="G65" t="s">
         <v>495</v>
-      </c>
-      <c r="B65" t="s">
-        <v>484</v>
-      </c>
-      <c r="D65" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B66" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C66" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D66" t="s">
         <v>23</v>
@@ -5647,13 +6215,13 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B67" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C67" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
@@ -5661,55 +6229,58 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B68" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C68" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B69" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C69" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C70" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D70" t="s">
-        <v>25</v>
+        <v>190</v>
+      </c>
+      <c r="G70" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C71" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D71" t="s">
         <v>23</v>
@@ -5717,13 +6288,13 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B72" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C72" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D72" t="s">
         <v>23</v>
@@ -5731,13 +6302,13 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B73" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C73" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
@@ -5745,72 +6316,529 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B74" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C74" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="C75" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>190</v>
+      </c>
+      <c r="G75" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B76" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="C76" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D76" t="s">
-        <v>25</v>
+        <v>190</v>
+      </c>
+      <c r="G76" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B77" t="s">
-        <v>542</v>
+        <v>571</v>
       </c>
       <c r="C77" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D77" t="s">
-        <v>25</v>
+        <v>190</v>
+      </c>
+      <c r="G77" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>563</v>
+      </c>
+      <c r="B78" t="s">
+        <v>539</v>
+      </c>
+      <c r="C78" t="s">
+        <v>548</v>
+      </c>
+      <c r="D78" t="s">
+        <v>190</v>
+      </c>
+      <c r="G78" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>663</v>
+      </c>
+      <c r="B79" t="s">
+        <v>566</v>
+      </c>
+      <c r="C79" t="s">
+        <v>577</v>
+      </c>
+      <c r="D79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>664</v>
+      </c>
+      <c r="B80" t="s">
         <v>567</v>
       </c>
-      <c r="B78" t="s">
-        <v>543</v>
-      </c>
-      <c r="C78" t="s">
-        <v>552</v>
-      </c>
-      <c r="D78" t="s">
-        <v>25</v>
+      <c r="C80" t="s">
+        <v>578</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>665</v>
+      </c>
+      <c r="B81" t="s">
+        <v>569</v>
+      </c>
+      <c r="C81" t="s">
+        <v>581</v>
+      </c>
+      <c r="D81" t="s">
+        <v>190</v>
+      </c>
+      <c r="G81" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>666</v>
+      </c>
+      <c r="B82" t="s">
+        <v>570</v>
+      </c>
+      <c r="C82" t="s">
+        <v>582</v>
+      </c>
+      <c r="D82" t="s">
+        <v>190</v>
+      </c>
+      <c r="E82">
+        <v>1956</v>
+      </c>
+      <c r="F82">
+        <v>2025</v>
+      </c>
+      <c r="G82" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>667</v>
+      </c>
+      <c r="B83" t="s">
+        <v>574</v>
+      </c>
+      <c r="C83" t="s">
+        <v>579</v>
+      </c>
+      <c r="D83" t="s">
+        <v>190</v>
+      </c>
+      <c r="G83" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>668</v>
+      </c>
+      <c r="B84" t="s">
+        <v>575</v>
+      </c>
+      <c r="C84" t="s">
+        <v>580</v>
+      </c>
+      <c r="D84" t="s">
+        <v>190</v>
+      </c>
+      <c r="G84" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>669</v>
+      </c>
+      <c r="B85" t="s">
+        <v>576</v>
+      </c>
+      <c r="C85" t="s">
+        <v>583</v>
+      </c>
+      <c r="D85" t="s">
+        <v>190</v>
+      </c>
+      <c r="G85" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>670</v>
+      </c>
+      <c r="B86" t="s">
+        <v>584</v>
+      </c>
+      <c r="C86" t="s">
+        <v>594</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>671</v>
+      </c>
+      <c r="B87" t="s">
+        <v>585</v>
+      </c>
+      <c r="C87" t="s">
+        <v>595</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>672</v>
+      </c>
+      <c r="B88" t="s">
+        <v>601</v>
+      </c>
+      <c r="C88" t="s">
+        <v>596</v>
+      </c>
+      <c r="D88" t="s">
+        <v>190</v>
+      </c>
+      <c r="E88">
+        <v>1957</v>
+      </c>
+      <c r="F88">
+        <v>2025</v>
+      </c>
+      <c r="G88" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>673</v>
+      </c>
+      <c r="B89" t="s">
+        <v>592</v>
+      </c>
+      <c r="C89" t="s">
+        <v>597</v>
+      </c>
+      <c r="D89" t="s">
+        <v>190</v>
+      </c>
+      <c r="G89" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>674</v>
+      </c>
+      <c r="B90" t="s">
+        <v>593</v>
+      </c>
+      <c r="C90" t="s">
+        <v>598</v>
+      </c>
+      <c r="D90" t="s">
+        <v>190</v>
+      </c>
+      <c r="G90" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>675</v>
+      </c>
+      <c r="B91" t="s">
+        <v>604</v>
+      </c>
+      <c r="C91" t="s">
+        <v>606</v>
+      </c>
+      <c r="D91" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>676</v>
+      </c>
+      <c r="B92" t="s">
+        <v>607</v>
+      </c>
+      <c r="D92" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>677</v>
+      </c>
+      <c r="B93" t="s">
+        <v>608</v>
+      </c>
+      <c r="D93" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>678</v>
+      </c>
+      <c r="B94" t="s">
+        <v>616</v>
+      </c>
+      <c r="C94" t="s">
+        <v>628</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>679</v>
+      </c>
+      <c r="B95" t="s">
+        <v>617</v>
+      </c>
+      <c r="C95" t="s">
+        <v>627</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>680</v>
+      </c>
+      <c r="B96" t="s">
+        <v>619</v>
+      </c>
+      <c r="C96" t="s">
+        <v>626</v>
+      </c>
+      <c r="D96" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>681</v>
+      </c>
+      <c r="B97" t="s">
+        <v>620</v>
+      </c>
+      <c r="C97" t="s">
+        <v>625</v>
+      </c>
+      <c r="D97" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>682</v>
+      </c>
+      <c r="B98" t="s">
+        <v>621</v>
+      </c>
+      <c r="C98" t="s">
+        <v>624</v>
+      </c>
+      <c r="D98" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>683</v>
+      </c>
+      <c r="B99" t="s">
+        <v>622</v>
+      </c>
+      <c r="C99" t="s">
+        <v>623</v>
+      </c>
+      <c r="D99" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>684</v>
+      </c>
+      <c r="B100" t="s">
+        <v>637</v>
+      </c>
+      <c r="C100" t="s">
+        <v>636</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100">
+        <v>1921</v>
+      </c>
+      <c r="F100">
+        <v>1995</v>
+      </c>
+      <c r="G100" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>685</v>
+      </c>
+      <c r="B101" t="s">
+        <v>638</v>
+      </c>
+      <c r="C101" t="s">
+        <v>651</v>
+      </c>
+      <c r="D101" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>686</v>
+      </c>
+      <c r="B102" t="s">
+        <v>639</v>
+      </c>
+      <c r="C102" t="s">
+        <v>650</v>
+      </c>
+      <c r="D102" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>687</v>
+      </c>
+      <c r="B103" t="s">
+        <v>640</v>
+      </c>
+      <c r="C103" t="s">
+        <v>649</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>688</v>
+      </c>
+      <c r="B104" t="s">
+        <v>641</v>
+      </c>
+      <c r="C104" t="s">
+        <v>648</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>689</v>
+      </c>
+      <c r="B105" t="s">
+        <v>642</v>
+      </c>
+      <c r="C105" t="s">
+        <v>647</v>
+      </c>
+      <c r="D105" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>690</v>
+      </c>
+      <c r="B106" t="s">
+        <v>643</v>
+      </c>
+      <c r="C106" t="s">
+        <v>646</v>
+      </c>
+      <c r="D106" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>691</v>
+      </c>
+      <c r="B107" t="s">
+        <v>644</v>
+      </c>
+      <c r="C107" t="s">
+        <v>645</v>
+      </c>
+      <c r="D107" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -5824,7 +6852,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -6299,7 +7327,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B23" t="s">
         <v>478</v>
@@ -6307,19 +7335,86 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B24" t="s">
+        <v>530</v>
+      </c>
+      <c r="C24" t="s">
         <v>531</v>
-      </c>
-      <c r="C24" t="s">
-        <v>532</v>
       </c>
       <c r="D24" t="s">
         <v>79</v>
       </c>
       <c r="E24">
         <v>1945</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>692</v>
+      </c>
+      <c r="B25" t="s">
+        <v>587</v>
+      </c>
+      <c r="C25" t="s">
+        <v>588</v>
+      </c>
+      <c r="D25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>693</v>
+      </c>
+      <c r="B26" t="s">
+        <v>589</v>
+      </c>
+      <c r="C26" t="s">
+        <v>590</v>
+      </c>
+      <c r="D26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>694</v>
+      </c>
+      <c r="B27" t="s">
+        <v>611</v>
+      </c>
+      <c r="C27" t="s">
+        <v>612</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>695</v>
+      </c>
+      <c r="B28" t="s">
+        <v>614</v>
+      </c>
+      <c r="C28" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>696</v>
+      </c>
+      <c r="B29" t="s">
+        <v>630</v>
+      </c>
+      <c r="C29" t="s">
+        <v>629</v>
       </c>
     </row>
   </sheetData>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5884DB-E312-A24E-A408-2D49DA4C50A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A95821-7493-B94D-91CF-9E28C03B1C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-8880" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="1157">
   <si>
     <t>怎么维护这个网站</t>
   </si>
@@ -1731,15 +1731,9 @@
     <t>Qin Wenyu</t>
   </si>
   <si>
-    <t>Pubuzhuoma;Zhaxidunzhu;Zhuoma;Luosangjiayang;Duojie</t>
-  </si>
-  <si>
     <t>Pubuzhuoma</t>
   </si>
   <si>
-    <t>Zhaxidunzhu</t>
-  </si>
-  <si>
     <t>Labadunzhu</t>
   </si>
   <si>
@@ -1827,9 +1821,6 @@
     <t>Feirt Zhouwa Sangmu</t>
   </si>
   <si>
-    <t>Zhaxidunzhu;Losang Choepel;Duoji;Luodan;Duobujie</t>
-  </si>
-  <si>
     <t>Losang Choepel</t>
   </si>
   <si>
@@ -1989,18 +1980,12 @@
     <t>Li Yang;Mingmacairen</t>
   </si>
   <si>
-    <t>Zhaxidunzhu;Losang Choepel;Puzhen;Pubuzhuoma;Dunzhuduoji</t>
-  </si>
-  <si>
     <t>115 min</t>
   </si>
   <si>
     <t>Red River Valley</t>
   </si>
   <si>
-    <t>雪豹;གསའ།</t>
-  </si>
-  <si>
     <t>Play My Dranyen</t>
   </si>
   <si>
@@ -2116,13 +2101,1408 @@
   </si>
   <si>
     <t>ORG-0028</t>
+  </si>
+  <si>
+    <t>雪豹</t>
+  </si>
+  <si>
+    <t>Wu Liben</t>
+  </si>
+  <si>
+    <t>吴立本</t>
+  </si>
+  <si>
+    <t>平息西藏叛乱</t>
+  </si>
+  <si>
+    <t>甘孜藏族人民的春天</t>
+  </si>
+  <si>
+    <t>拉萨河畔</t>
+  </si>
+  <si>
+    <t>康巴的新生</t>
+  </si>
+  <si>
+    <t>甘孜藏族人民的控诉</t>
+  </si>
+  <si>
+    <t>Peaceful Suppression of Rebellion</t>
+  </si>
+  <si>
+    <t>The Horse Thief</t>
+  </si>
+  <si>
+    <t>盗马贼</t>
+  </si>
+  <si>
+    <t>阳光照耀山南</t>
+  </si>
+  <si>
+    <t>Yang Cai</t>
+  </si>
+  <si>
+    <t>杨采</t>
+  </si>
+  <si>
+    <t>孔繁森</t>
+  </si>
+  <si>
+    <t>Kong Fansen</t>
+  </si>
+  <si>
+    <t>Chen Guoxing;Wang Ping</t>
+  </si>
+  <si>
+    <t>Wang Xingdong</t>
+  </si>
+  <si>
+    <t>Gao Ming;Jiang Yaofen</t>
+  </si>
+  <si>
+    <t>Chen Guoxing</t>
+  </si>
+  <si>
+    <t>Wang Ping</t>
+  </si>
+  <si>
+    <t>Gao Ming</t>
+  </si>
+  <si>
+    <t>Jiang Yaofen</t>
+  </si>
+  <si>
+    <t>蒋耀玢</t>
+  </si>
+  <si>
+    <t>高明</t>
+  </si>
+  <si>
+    <t>王兴东</t>
+  </si>
+  <si>
+    <t>王坪</t>
+  </si>
+  <si>
+    <t>陈国星</t>
+  </si>
+  <si>
+    <t>112 min</t>
+  </si>
+  <si>
+    <t>China: June 17, 1996</t>
+  </si>
+  <si>
+    <t>Beijing Film Studio;Shandong Film Studio</t>
+  </si>
+  <si>
+    <t>Shandong Film Studio</t>
+  </si>
+  <si>
+    <t>山东电影制片厂</t>
+  </si>
+  <si>
+    <t>A New Life in Kham</t>
+  </si>
+  <si>
+    <t>On the Banks of the Lhasa River</t>
+  </si>
+  <si>
+    <t>Sunshine over Shannan</t>
+  </si>
+  <si>
+    <t>The Tibetan People of Garzê Speak Out</t>
+  </si>
+  <si>
+    <t>Springtime for the Tibetan People of Garzê</t>
+  </si>
+  <si>
+    <t>FILM-0049</t>
+  </si>
+  <si>
+    <t>FILM-0050</t>
+  </si>
+  <si>
+    <t>FILM-0051</t>
+  </si>
+  <si>
+    <t>FILM-0052</t>
+  </si>
+  <si>
+    <t>FILM-0053</t>
+  </si>
+  <si>
+    <t>FILM-0054</t>
+  </si>
+  <si>
+    <t>FILM-0055</t>
+  </si>
+  <si>
+    <t>FILM-0056</t>
+  </si>
+  <si>
+    <t>战胜怒江</t>
+  </si>
+  <si>
+    <t>康藏青藏公路修建和通车</t>
+  </si>
+  <si>
+    <t>达赖喇嘛、班禅大师参观祖国各地</t>
+  </si>
+  <si>
+    <t>庆祝西藏自治区筹备委员会成立</t>
+  </si>
+  <si>
+    <t>庆祝西藏自治区成立十周年</t>
+  </si>
+  <si>
+    <t>Wu Jun</t>
+  </si>
+  <si>
+    <t>吴均</t>
+  </si>
+  <si>
+    <t>欢腾的西藏</t>
+  </si>
+  <si>
+    <t>Liu Wenmiao</t>
+  </si>
+  <si>
+    <t>刘文渺</t>
+  </si>
+  <si>
+    <t>Shen Shan</t>
+  </si>
+  <si>
+    <t>沈剡</t>
+  </si>
+  <si>
+    <t>班禅大师在生命的最后时刻</t>
+  </si>
+  <si>
+    <t>登上希夏邦马峰</t>
+  </si>
+  <si>
+    <t>Summit Memory</t>
+  </si>
+  <si>
+    <t>巅峰记忆</t>
+  </si>
+  <si>
+    <t>遥远的普若岗日</t>
+  </si>
+  <si>
+    <t>95 min</t>
+  </si>
+  <si>
+    <t>Beyond the Frozen Horizon</t>
+  </si>
+  <si>
+    <t>Zhao Hantang;Cai Yu</t>
+  </si>
+  <si>
+    <t>Cai Yu</t>
+  </si>
+  <si>
+    <t>Tang Shiyi;Awangrenqing;Wangzhuocuo</t>
+  </si>
+  <si>
+    <t>China: December 16, 2025</t>
+  </si>
+  <si>
+    <t>Tibet Film and Television Culture Co., Ltd.</t>
+  </si>
+  <si>
+    <t>西藏影视文化有限公司</t>
+  </si>
+  <si>
+    <t>我的喜马拉雅</t>
+  </si>
+  <si>
+    <t>My Himalayas</t>
+  </si>
+  <si>
+    <t>Zhang Xin</t>
+  </si>
+  <si>
+    <t>Wu Mengzhang</t>
+  </si>
+  <si>
+    <t>Wu Mengzhang;Chang You</t>
+  </si>
+  <si>
+    <t>Renqingdunzhu;Wangzhuocuo;Cideji</t>
+  </si>
+  <si>
+    <t>China: October 6, 2019</t>
+  </si>
+  <si>
+    <t>Chang You</t>
+  </si>
+  <si>
+    <t>Renqingdunzhu</t>
+  </si>
+  <si>
+    <t>Cideji</t>
+  </si>
+  <si>
+    <t>次德吉</t>
+  </si>
+  <si>
+    <t>旺卓措</t>
+  </si>
+  <si>
+    <t>Wangzhuocuo</t>
+  </si>
+  <si>
+    <t>仁青顿珠</t>
+  </si>
+  <si>
+    <t>畅游</t>
+  </si>
+  <si>
+    <t>吴孟璋</t>
+  </si>
+  <si>
+    <t>张鑫</t>
+  </si>
+  <si>
+    <t>Zhao Hantang</t>
+  </si>
+  <si>
+    <t>Tang Shiyi</t>
+  </si>
+  <si>
+    <t>Awangrenqing</t>
+  </si>
+  <si>
+    <t>阿旺仁青</t>
+  </si>
+  <si>
+    <t>唐诗逸</t>
+  </si>
+  <si>
+    <t>蔡宇</t>
+  </si>
+  <si>
+    <t>赵汉唐</t>
+  </si>
+  <si>
+    <t>回西藏</t>
+  </si>
+  <si>
+    <t>Kong and Jinme</t>
+  </si>
+  <si>
+    <t>天宝</t>
+  </si>
+  <si>
+    <t>Tian Bao</t>
+  </si>
+  <si>
+    <t>116 min</t>
+  </si>
+  <si>
+    <t>Himalaya: Ladder to Paradise</t>
+  </si>
+  <si>
+    <t>喜马拉雅天梯</t>
+  </si>
+  <si>
+    <t>看不见的顶峰</t>
+  </si>
+  <si>
+    <t>Invisible Summit</t>
+  </si>
+  <si>
+    <t>西藏喜开丰收镰</t>
+  </si>
+  <si>
+    <t>西藏高原引种冬小麦成功</t>
+  </si>
+  <si>
+    <t>飞越天险</t>
+  </si>
+  <si>
+    <t>Li Enjie</t>
+  </si>
+  <si>
+    <t>Chen Ge</t>
+  </si>
+  <si>
+    <t>Zhang Haoran</t>
+  </si>
+  <si>
+    <t>Li Ziping</t>
+  </si>
+  <si>
+    <t>Zhou Senguan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shi Meifen </t>
+  </si>
+  <si>
+    <t>Yu Yang</t>
+  </si>
+  <si>
+    <t>于洋</t>
+  </si>
+  <si>
+    <t>石美芬</t>
+  </si>
+  <si>
+    <t>周森冠</t>
+  </si>
+  <si>
+    <t>李紫平</t>
+  </si>
+  <si>
+    <t>张浩然</t>
+  </si>
+  <si>
+    <t>陈戈</t>
+  </si>
+  <si>
+    <t>李恩杰</t>
+  </si>
+  <si>
+    <t>Zhang Hairan;Li Ziping;Zhou Senguan;Shi Meifen;Yu Yang</t>
+  </si>
+  <si>
+    <t>冰风暴</t>
+  </si>
+  <si>
+    <t>Wings Over Everest</t>
+  </si>
+  <si>
+    <t>110 min</t>
+  </si>
+  <si>
+    <t>Fay Yu</t>
+  </si>
+  <si>
+    <t>今日西藏</t>
+  </si>
+  <si>
+    <t>Li Kun</t>
+  </si>
+  <si>
+    <t>李堃</t>
+  </si>
+  <si>
+    <t>再次登上珠穆朗玛峰</t>
+  </si>
+  <si>
+    <t>放下武器以后</t>
+  </si>
+  <si>
+    <t>征服世界最高峰</t>
+  </si>
+  <si>
+    <t>44 min</t>
+  </si>
+  <si>
+    <t>Wang Fuzhou;Liu Lianman</t>
+  </si>
+  <si>
+    <t>Wang Fuzhou</t>
+  </si>
+  <si>
+    <t>Liu Lianman</t>
+  </si>
+  <si>
+    <t>刘连满</t>
+  </si>
+  <si>
+    <t>王富洲</t>
+  </si>
+  <si>
+    <t>征服冰山之父</t>
+  </si>
+  <si>
+    <t>Wang Wei</t>
+  </si>
+  <si>
+    <t>王伟</t>
+  </si>
+  <si>
+    <t>高原红四连</t>
+  </si>
+  <si>
+    <t>无限风光在险峰</t>
+  </si>
+  <si>
+    <t>Shanghai Film Studio</t>
+  </si>
+  <si>
+    <t>上海电影制片厂</t>
+  </si>
+  <si>
+    <t>On Perilous Peaks Dwells Beauty in Her Infinite Variety</t>
+  </si>
+  <si>
+    <t>西藏高原大寨花</t>
+  </si>
+  <si>
+    <t>为了和平解决中印边境问题</t>
+  </si>
+  <si>
+    <t>1962年中印边界战争</t>
+  </si>
+  <si>
+    <t>中印边界战争秘史</t>
+  </si>
+  <si>
+    <t>Sino-Indian War Secret History</t>
+  </si>
+  <si>
+    <t>主动停火主动后撤</t>
+  </si>
+  <si>
+    <t>中印自卫反击战亲历记</t>
+  </si>
+  <si>
+    <t>欢腾的西藏物交会</t>
+  </si>
+  <si>
+    <t>农奴翻身见太阳</t>
+  </si>
+  <si>
+    <t>自卫反击</t>
+  </si>
+  <si>
+    <t>Zhai Chao;Wen Zonghua;Lu Fang</t>
+  </si>
+  <si>
+    <t>Zhao Chao</t>
+  </si>
+  <si>
+    <t>Wen Zonghua</t>
+  </si>
+  <si>
+    <t>Lu Fang</t>
+  </si>
+  <si>
+    <t>陆方</t>
+  </si>
+  <si>
+    <t>文宗华</t>
+  </si>
+  <si>
+    <t>翟超</t>
+  </si>
+  <si>
+    <t>交还印军军用物资</t>
+  </si>
+  <si>
+    <t>世界屋脊的形成</t>
+  </si>
+  <si>
+    <t>Shanghai Science and Educational Film Studio</t>
+  </si>
+  <si>
+    <t>上海科学教育电影制片厂</t>
+  </si>
+  <si>
+    <t>世界屋脊的歌声</t>
+  </si>
+  <si>
+    <t>A Chinese Anthem from the Roof of the World</t>
+  </si>
+  <si>
+    <t>世界屋脊的太阳</t>
+  </si>
+  <si>
+    <t>Sun of the Roof of the World</t>
+  </si>
+  <si>
+    <t>世界屋脊的传说</t>
+  </si>
+  <si>
+    <t>Li Zexiang</t>
+  </si>
+  <si>
+    <t>李则翔</t>
+  </si>
+  <si>
+    <t>西藏的江南</t>
+  </si>
+  <si>
+    <t>西藏的天空</t>
+  </si>
+  <si>
+    <t>China: October 1, 1974</t>
+  </si>
+  <si>
+    <t>世界屋脊</t>
+  </si>
+  <si>
+    <t>61 min</t>
+  </si>
+  <si>
+    <t>Yin Peilong</t>
+  </si>
+  <si>
+    <t>殷培龙</t>
+  </si>
+  <si>
+    <t>泥石流</t>
+  </si>
+  <si>
+    <t>日光城</t>
+  </si>
+  <si>
+    <t>故乡行</t>
+  </si>
+  <si>
+    <t>拉普次旺多吉</t>
+  </si>
+  <si>
+    <t>珠峰之歌</t>
+  </si>
+  <si>
+    <t>藏医藏药</t>
+  </si>
+  <si>
+    <t>青藏路掠影</t>
+  </si>
+  <si>
+    <t>南迦巴瓦峰科学考察</t>
+  </si>
+  <si>
+    <t>拉萨一人家</t>
+  </si>
+  <si>
+    <t>西藏西藏</t>
+  </si>
+  <si>
+    <t>绿色的墨脱</t>
+  </si>
+  <si>
+    <t>我的家乡西藏</t>
+  </si>
+  <si>
+    <t>日喀则</t>
+  </si>
+  <si>
+    <t>扎什伦布寺</t>
+  </si>
+  <si>
+    <t>Conquering the Nu River</t>
+  </si>
+  <si>
+    <t>The Construction and Opening of the Kang–Tibet and Qinghai–Tibet Highways</t>
+  </si>
+  <si>
+    <t>The Dalai Lama and the Panchen Lama Visit Different Parts of the Motherland</t>
+  </si>
+  <si>
+    <t>Celebrating the Establishment of the Preparatory Committee for the Tibet Autonomous Region</t>
+  </si>
+  <si>
+    <t>Celebrating the Tenth Anniversary of the Establishment of the Tibet Autonomous Region</t>
+  </si>
+  <si>
+    <t>Tibet in Celebration</t>
+  </si>
+  <si>
+    <t>The Last Moments of the Panchen Lama's Life</t>
+  </si>
+  <si>
+    <t>The Ascent of Shishapangma</t>
+  </si>
+  <si>
+    <t>Tibet Celebrates the Harvest</t>
+  </si>
+  <si>
+    <t>Successful Introduction of Winter Wheat to the Tibetan Plateau</t>
+  </si>
+  <si>
+    <t>Flying over Natural Barriers</t>
+  </si>
+  <si>
+    <t>Tibet Today</t>
+  </si>
+  <si>
+    <t>Climbing Mount Everest Again</t>
+  </si>
+  <si>
+    <t>After Laying Down Arms</t>
+  </si>
+  <si>
+    <t>Conquering the World's Highest Peak</t>
+  </si>
+  <si>
+    <t>Conquering the Father of Ice Mountains</t>
+  </si>
+  <si>
+    <t>The Fourth Red Company on the Plateau</t>
+  </si>
+  <si>
+    <t>The Dazhai Flower on the Tibetan Plateau</t>
+  </si>
+  <si>
+    <t>For the Peaceful Settlement of the Sino-Indian Border Dispute</t>
+  </si>
+  <si>
+    <t>The 1962 Sino-Indian Border War</t>
+  </si>
+  <si>
+    <t>Voluntary Ceasefire and Withdrawal</t>
+  </si>
+  <si>
+    <t>Eyewitness Accounts of the Sino-Indian Self-Defense Counterattack</t>
+  </si>
+  <si>
+    <t>The Lively Tibet Trade Fair</t>
+  </si>
+  <si>
+    <t>Emancipated Serfs See the Sun</t>
+  </si>
+  <si>
+    <t>Counterattack in Self-Defense</t>
+  </si>
+  <si>
+    <t>Returning Military Supplies to the Indian Army</t>
+  </si>
+  <si>
+    <t>The Formation of the Roof of the World</t>
+  </si>
+  <si>
+    <t>Legends of the Roof of the World</t>
+  </si>
+  <si>
+    <t>The Jiangnan of Tibet</t>
+  </si>
+  <si>
+    <t>The Sky over Tibe</t>
+  </si>
+  <si>
+    <t>The Roof of the World</t>
+  </si>
+  <si>
+    <t>Yin Hong</t>
+  </si>
+  <si>
+    <t>殷红</t>
+  </si>
+  <si>
+    <t>第三极</t>
+  </si>
+  <si>
+    <t>Roof of the World</t>
+  </si>
+  <si>
+    <t>46 min</t>
+  </si>
+  <si>
+    <t>Zeng Hairuo</t>
+  </si>
+  <si>
+    <t>曾海若</t>
+  </si>
+  <si>
+    <t>Tashi Wangdu</t>
+  </si>
+  <si>
+    <t>扎西旺堆</t>
+  </si>
+  <si>
+    <t>Tashi Dhondup</t>
+  </si>
+  <si>
+    <t>Pubuzhuoma;Tashi Dhondup;Zhuoma;Luosangjiayang;Duojie</t>
+  </si>
+  <si>
+    <t>Tashi Dhondup;Losang Choepel;Puzhen;Pubuzhuoma;Dunzhuduoji</t>
+  </si>
+  <si>
+    <t>Tashi Dhondup;Losang Choepel;Duoji;Luodan;Duobujie</t>
+  </si>
+  <si>
+    <t>攀登者</t>
+  </si>
+  <si>
+    <t>125 min</t>
+  </si>
+  <si>
+    <t>The Climbers</t>
+  </si>
+  <si>
+    <t>Words of Everest</t>
+  </si>
+  <si>
+    <t>Paul Copeland</t>
+  </si>
+  <si>
+    <t>珠峰队长</t>
+  </si>
+  <si>
+    <t>The Everest Captain</t>
+  </si>
+  <si>
+    <t>Everest</t>
+  </si>
+  <si>
+    <t>120 min</t>
+  </si>
+  <si>
+    <t>青藏公路全线通车</t>
+  </si>
+  <si>
+    <t>20 min</t>
+  </si>
+  <si>
+    <t>Fu Ya</t>
+  </si>
+  <si>
+    <t>傅亚</t>
+  </si>
+  <si>
+    <t>Manchu</t>
+  </si>
+  <si>
+    <t>天幕</t>
+  </si>
+  <si>
+    <t>Skye Rise</t>
+  </si>
+  <si>
+    <t>青藏线</t>
+  </si>
+  <si>
+    <t>The Qinghai-Tibet Line</t>
+  </si>
+  <si>
+    <t>99 min</t>
+  </si>
+  <si>
+    <t>117 min</t>
+  </si>
+  <si>
+    <t>Nanga Parbat</t>
+  </si>
+  <si>
+    <t>Joseph Vilsmaier</t>
+  </si>
+  <si>
+    <t>拉萨祈祷大法会</t>
+  </si>
+  <si>
+    <t>西藏大祈愿</t>
+  </si>
+  <si>
+    <t>58 min</t>
+  </si>
+  <si>
+    <t>Great Prayrt Festival of Lhasa</t>
+  </si>
+  <si>
+    <t>Chen Zhen;Li Ying</t>
+  </si>
+  <si>
+    <t>Chen Zhen</t>
+  </si>
+  <si>
+    <t>Li Ying</t>
+  </si>
+  <si>
+    <t>李缨</t>
+  </si>
+  <si>
+    <t>陈真</t>
+  </si>
+  <si>
+    <t>欢腾的拉萨</t>
+  </si>
+  <si>
+    <t>17 min</t>
+  </si>
+  <si>
+    <t>Lhasa in Celebration</t>
+  </si>
+  <si>
+    <t>情深日喀则</t>
+  </si>
+  <si>
+    <t>Li Pengfei</t>
+  </si>
+  <si>
+    <t>Shi Yike</t>
+  </si>
+  <si>
+    <t>史壹可</t>
+  </si>
+  <si>
+    <t>李鹏飞</t>
+  </si>
+  <si>
+    <t>Tashi Lhunpo Monastery</t>
+  </si>
+  <si>
+    <t>Deep Affection for Shigatse</t>
+  </si>
+  <si>
+    <t>The Opening of the Entire Qinghai–Tibet Highway</t>
+  </si>
+  <si>
+    <t>Tibet, My Homeland</t>
+  </si>
+  <si>
+    <t>Shigatse</t>
+  </si>
+  <si>
+    <t>Debris Flow</t>
+  </si>
+  <si>
+    <t>The City of Sunshine</t>
+  </si>
+  <si>
+    <t>A Journey Home</t>
+  </si>
+  <si>
+    <t>Lhapu Tsewang Dorje</t>
+  </si>
+  <si>
+    <t>Song of Mount Everest</t>
+  </si>
+  <si>
+    <t>Tibetan Medicine and Medicinal Herbs</t>
+  </si>
+  <si>
+    <t>Glimpses of the Qinghai–Tibet Highway</t>
+  </si>
+  <si>
+    <t>Scientific Expedition to Namcha Barwa</t>
+  </si>
+  <si>
+    <t>A Family in Lhasa</t>
+  </si>
+  <si>
+    <t>Tibet, Tibet</t>
+  </si>
+  <si>
+    <t>Green Metog</t>
+  </si>
+  <si>
+    <t>The Great Prayer Festival in Lhasa</t>
+  </si>
+  <si>
+    <t>FILM-0057</t>
+  </si>
+  <si>
+    <t>FILM-0058</t>
+  </si>
+  <si>
+    <t>FILM-0059</t>
+  </si>
+  <si>
+    <t>FILM-0060</t>
+  </si>
+  <si>
+    <t>FILM-0061</t>
+  </si>
+  <si>
+    <t>FILM-0062</t>
+  </si>
+  <si>
+    <t>FILM-0063</t>
+  </si>
+  <si>
+    <t>FILM-0064</t>
+  </si>
+  <si>
+    <t>FILM-0065</t>
+  </si>
+  <si>
+    <t>FILM-0066</t>
+  </si>
+  <si>
+    <t>FILM-0067</t>
+  </si>
+  <si>
+    <t>FILM-0068</t>
+  </si>
+  <si>
+    <t>FILM-0069</t>
+  </si>
+  <si>
+    <t>FILM-0070</t>
+  </si>
+  <si>
+    <t>FILM-0071</t>
+  </si>
+  <si>
+    <t>FILM-0072</t>
+  </si>
+  <si>
+    <t>FILM-0073</t>
+  </si>
+  <si>
+    <t>FILM-0074</t>
+  </si>
+  <si>
+    <t>FILM-0075</t>
+  </si>
+  <si>
+    <t>FILM-0076</t>
+  </si>
+  <si>
+    <t>FILM-0077</t>
+  </si>
+  <si>
+    <t>FILM-0078</t>
+  </si>
+  <si>
+    <t>FILM-0079</t>
+  </si>
+  <si>
+    <t>FILM-0080</t>
+  </si>
+  <si>
+    <t>FILM-0081</t>
+  </si>
+  <si>
+    <t>FILM-0082</t>
+  </si>
+  <si>
+    <t>FILM-0083</t>
+  </si>
+  <si>
+    <t>FILM-0084</t>
+  </si>
+  <si>
+    <t>FILM-0085</t>
+  </si>
+  <si>
+    <t>FILM-0086</t>
+  </si>
+  <si>
+    <t>FILM-0087</t>
+  </si>
+  <si>
+    <t>FILM-0088</t>
+  </si>
+  <si>
+    <t>FILM-0089</t>
+  </si>
+  <si>
+    <t>FILM-0090</t>
+  </si>
+  <si>
+    <t>FILM-0091</t>
+  </si>
+  <si>
+    <t>FILM-0092</t>
+  </si>
+  <si>
+    <t>FILM-0093</t>
+  </si>
+  <si>
+    <t>FILM-0094</t>
+  </si>
+  <si>
+    <t>FILM-0095</t>
+  </si>
+  <si>
+    <t>FILM-0096</t>
+  </si>
+  <si>
+    <t>FILM-0097</t>
+  </si>
+  <si>
+    <t>FILM-0098</t>
+  </si>
+  <si>
+    <t>FILM-0099</t>
+  </si>
+  <si>
+    <t>FILM-0100</t>
+  </si>
+  <si>
+    <t>FILM-0101</t>
+  </si>
+  <si>
+    <t>FILM-0102</t>
+  </si>
+  <si>
+    <t>FILM-0103</t>
+  </si>
+  <si>
+    <t>FILM-0104</t>
+  </si>
+  <si>
+    <t>FILM-0105</t>
+  </si>
+  <si>
+    <t>FILM-0106</t>
+  </si>
+  <si>
+    <t>FILM-0107</t>
+  </si>
+  <si>
+    <t>FILM-0108</t>
+  </si>
+  <si>
+    <t>FILM-0109</t>
+  </si>
+  <si>
+    <t>FILM-0110</t>
+  </si>
+  <si>
+    <t>FILM-0111</t>
+  </si>
+  <si>
+    <t>FILM-0112</t>
+  </si>
+  <si>
+    <t>FILM-0113</t>
+  </si>
+  <si>
+    <t>FILM-0114</t>
+  </si>
+  <si>
+    <t>FILM-0115</t>
+  </si>
+  <si>
+    <t>FILM-0116</t>
+  </si>
+  <si>
+    <t>FILM-0117</t>
+  </si>
+  <si>
+    <t>FILM-0118</t>
+  </si>
+  <si>
+    <t>FILM-0119</t>
+  </si>
+  <si>
+    <t>FILM-0120</t>
+  </si>
+  <si>
+    <t>FILM-0121</t>
+  </si>
+  <si>
+    <t>FILM-0122</t>
+  </si>
+  <si>
+    <t>FILM-0123</t>
+  </si>
+  <si>
+    <t>FILM-0124</t>
+  </si>
+  <si>
+    <t>FILM-0125</t>
+  </si>
+  <si>
+    <t>FILM-0126</t>
+  </si>
+  <si>
+    <t>PERSON-0108</t>
+  </si>
+  <si>
+    <t>PERSON-0109</t>
+  </si>
+  <si>
+    <t>PERSON-0110</t>
+  </si>
+  <si>
+    <t>PERSON-0111</t>
+  </si>
+  <si>
+    <t>PERSON-0112</t>
+  </si>
+  <si>
+    <t>PERSON-0113</t>
+  </si>
+  <si>
+    <t>PERSON-0114</t>
+  </si>
+  <si>
+    <t>PERSON-0115</t>
+  </si>
+  <si>
+    <t>PERSON-0116</t>
+  </si>
+  <si>
+    <t>PERSON-0117</t>
+  </si>
+  <si>
+    <t>PERSON-0118</t>
+  </si>
+  <si>
+    <t>PERSON-0119</t>
+  </si>
+  <si>
+    <t>PERSON-0120</t>
+  </si>
+  <si>
+    <t>PERSON-0121</t>
+  </si>
+  <si>
+    <t>PERSON-0122</t>
+  </si>
+  <si>
+    <t>PERSON-0123</t>
+  </si>
+  <si>
+    <t>PERSON-0124</t>
+  </si>
+  <si>
+    <t>PERSON-0125</t>
+  </si>
+  <si>
+    <t>PERSON-0126</t>
+  </si>
+  <si>
+    <t>PERSON-0127</t>
+  </si>
+  <si>
+    <t>PERSON-0128</t>
+  </si>
+  <si>
+    <t>PERSON-0129</t>
+  </si>
+  <si>
+    <t>PERSON-0130</t>
+  </si>
+  <si>
+    <t>PERSON-0131</t>
+  </si>
+  <si>
+    <t>PERSON-0132</t>
+  </si>
+  <si>
+    <t>PERSON-0133</t>
+  </si>
+  <si>
+    <t>PERSON-0134</t>
+  </si>
+  <si>
+    <t>PERSON-0135</t>
+  </si>
+  <si>
+    <t>PERSON-0136</t>
+  </si>
+  <si>
+    <t>PERSON-0137</t>
+  </si>
+  <si>
+    <t>PERSON-0138</t>
+  </si>
+  <si>
+    <t>PERSON-0139</t>
+  </si>
+  <si>
+    <t>PERSON-0140</t>
+  </si>
+  <si>
+    <t>PERSON-0141</t>
+  </si>
+  <si>
+    <t>PERSON-0142</t>
+  </si>
+  <si>
+    <t>PERSON-0143</t>
+  </si>
+  <si>
+    <t>PERSON-0144</t>
+  </si>
+  <si>
+    <t>PERSON-0145</t>
+  </si>
+  <si>
+    <t>PERSON-0146</t>
+  </si>
+  <si>
+    <t>PERSON-0147</t>
+  </si>
+  <si>
+    <t>PERSON-0148</t>
+  </si>
+  <si>
+    <t>PERSON-0149</t>
+  </si>
+  <si>
+    <t>PERSON-0150</t>
+  </si>
+  <si>
+    <t>PERSON-0151</t>
+  </si>
+  <si>
+    <t>PERSON-0152</t>
+  </si>
+  <si>
+    <t>PERSON-0153</t>
+  </si>
+  <si>
+    <t>PERSON-0154</t>
+  </si>
+  <si>
+    <t>ORG-0029</t>
+  </si>
+  <si>
+    <t>ORG-0030</t>
+  </si>
+  <si>
+    <t>ORG-0031</t>
+  </si>
+  <si>
+    <t>ORG-0032</t>
+  </si>
+  <si>
+    <t>西藏往事</t>
+  </si>
+  <si>
+    <t>96 min</t>
+  </si>
+  <si>
+    <t>Once Upon a Time in Tibet</t>
+  </si>
+  <si>
+    <t>FILM-0127</t>
+  </si>
+  <si>
+    <t>康定情歌</t>
+  </si>
+  <si>
+    <t>105 min</t>
+  </si>
+  <si>
+    <t>雅安边茶</t>
+  </si>
+  <si>
+    <t>康人生活</t>
+  </si>
+  <si>
+    <t>西康跳神</t>
+  </si>
+  <si>
+    <t>西康一瞥</t>
+  </si>
+  <si>
+    <t>喇嘛生活</t>
+  </si>
+  <si>
+    <t>Sun Mingjing</t>
+  </si>
+  <si>
+    <t>孙明经</t>
+  </si>
+  <si>
+    <t>猛河的黎明</t>
+  </si>
+  <si>
+    <t>Dawn of Meng River</t>
+  </si>
+  <si>
+    <t>The Gold and Silver River Band</t>
+  </si>
+  <si>
+    <t>金银滩</t>
+  </si>
+  <si>
+    <t>103 min</t>
+  </si>
+  <si>
+    <t>Ling Zifeng</t>
+  </si>
+  <si>
+    <t>凌子风</t>
+  </si>
+  <si>
+    <t>FILM-0128</t>
+  </si>
+  <si>
+    <t>FILM-0129</t>
+  </si>
+  <si>
+    <t>FILM-0130</t>
+  </si>
+  <si>
+    <t>FILM-0131</t>
+  </si>
+  <si>
+    <t>FILM-0132</t>
+  </si>
+  <si>
+    <t>FILM-0133</t>
+  </si>
+  <si>
+    <t>FILM-0134</t>
+  </si>
+  <si>
+    <t>FILM-0135</t>
+  </si>
+  <si>
+    <t>PERSON-0155</t>
+  </si>
+  <si>
+    <t>PERSON-0156</t>
+  </si>
+  <si>
+    <t>Hui</t>
+  </si>
+  <si>
+    <t>Kangding Love Song</t>
+  </si>
+  <si>
+    <t>Ya'an Border Tea</t>
+  </si>
+  <si>
+    <t>Life of the People of Kham</t>
+  </si>
+  <si>
+    <t>Ritual Cham Dances in Xikang</t>
+  </si>
+  <si>
+    <t>A Glimpse of Xikang</t>
+  </si>
+  <si>
+    <t>Life of Tibetan Lamas</t>
+  </si>
+  <si>
+    <t>雪域明珠-西藏文化展</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shining Pearl of the Snowland: China Tibetan Culture Exhibition </t>
+  </si>
+  <si>
+    <t>Beijing Film Developing and Video Technology Factory</t>
+  </si>
+  <si>
+    <t>北京电影洗印录像技术厂</t>
+  </si>
+  <si>
+    <t>西藏今昔</t>
+  </si>
+  <si>
+    <t>Tibet Past and Present</t>
+  </si>
+  <si>
+    <t>今日中国我们的拉萨</t>
+  </si>
+  <si>
+    <t>China Today, Our Lhasa</t>
+  </si>
+  <si>
+    <t>FILM-0136</t>
+  </si>
+  <si>
+    <t>FILM-0137</t>
+  </si>
+  <si>
+    <t>FILM-0138</t>
+  </si>
+  <si>
+    <t>ORG-0033</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2132,6 +3512,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2157,8 +3544,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2599,7 +3987,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:R139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -3802,11 +5190,17 @@
       <c r="F23" t="s">
         <v>51</v>
       </c>
+      <c r="I23" t="s">
+        <v>693</v>
+      </c>
       <c r="M23" t="s">
         <v>79</v>
       </c>
       <c r="N23" t="s">
         <v>123</v>
+      </c>
+      <c r="P23" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
@@ -4272,7 +5666,7 @@
         <v>510</v>
       </c>
       <c r="B40" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C40" t="s">
         <v>503</v>
@@ -4296,7 +5690,7 @@
         <v>567</v>
       </c>
       <c r="K40" t="s">
-        <v>568</v>
+        <v>928</v>
       </c>
       <c r="M40" t="s">
         <v>79</v>
@@ -4313,7 +5707,7 @@
         <v>511</v>
       </c>
       <c r="B41" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C41" t="s">
         <v>504</v>
@@ -4331,13 +5725,13 @@
         <v>21</v>
       </c>
       <c r="I41" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="J41" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="K41" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="M41" t="s">
         <v>79</v>
@@ -4346,7 +5740,7 @@
         <v>123</v>
       </c>
       <c r="P41" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
@@ -4354,7 +5748,7 @@
         <v>512</v>
       </c>
       <c r="B42" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C42" t="s">
         <v>505</v>
@@ -4363,7 +5757,7 @@
         <v>1988</v>
       </c>
       <c r="E42" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F42" t="s">
         <v>38</v>
@@ -4372,13 +5766,13 @@
         <v>21</v>
       </c>
       <c r="I42" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="J42" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="K42" t="s">
-        <v>654</v>
+        <v>929</v>
       </c>
       <c r="M42" t="s">
         <v>79</v>
@@ -4392,7 +5786,7 @@
         <v>513</v>
       </c>
       <c r="B43" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C43" t="s">
         <v>506</v>
@@ -4418,7 +5812,7 @@
         <v>514</v>
       </c>
       <c r="B44" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C44" t="s">
         <v>507</v>
@@ -4433,22 +5827,22 @@
         <v>21</v>
       </c>
       <c r="I44" t="s">
+        <v>582</v>
+      </c>
+      <c r="J44" t="s">
+        <v>583</v>
+      </c>
+      <c r="K44" t="s">
+        <v>930</v>
+      </c>
+      <c r="M44" t="s">
+        <v>79</v>
+      </c>
+      <c r="N44" t="s">
         <v>584</v>
       </c>
-      <c r="J44" t="s">
-        <v>585</v>
-      </c>
-      <c r="K44" t="s">
-        <v>600</v>
-      </c>
-      <c r="M44" t="s">
-        <v>79</v>
-      </c>
-      <c r="N44" t="s">
-        <v>586</v>
-      </c>
       <c r="P44" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -4456,7 +5850,7 @@
         <v>515</v>
       </c>
       <c r="B45" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C45" t="s">
         <v>508</v>
@@ -4465,7 +5859,7 @@
         <v>1996</v>
       </c>
       <c r="E45" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="F45" t="s">
         <v>38</v>
@@ -4482,7 +5876,7 @@
         <v>516</v>
       </c>
       <c r="B46" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C46" t="s">
         <v>509</v>
@@ -4549,19 +5943,19 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B48" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C48" t="s">
-        <v>657</v>
+        <v>692</v>
       </c>
       <c r="D48">
         <v>2023</v>
       </c>
       <c r="E48" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F48" t="s">
         <v>38</v>
@@ -4570,36 +5964,36 @@
         <v>21</v>
       </c>
       <c r="I48" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="J48" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="K48" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="L48" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M48" t="s">
         <v>79</v>
       </c>
       <c r="N48" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P48" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B49" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C49" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D49">
         <v>1956</v>
@@ -4611,6 +6005,2124 @@
         <v>123</v>
       </c>
       <c r="P49" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>730</v>
+      </c>
+      <c r="B50" t="s">
+        <v>700</v>
+      </c>
+      <c r="C50" t="s">
+        <v>695</v>
+      </c>
+      <c r="D50">
+        <v>1959</v>
+      </c>
+      <c r="M50" t="s">
+        <v>79</v>
+      </c>
+      <c r="N50" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>731</v>
+      </c>
+      <c r="B51" t="s">
+        <v>729</v>
+      </c>
+      <c r="C51" t="s">
+        <v>696</v>
+      </c>
+      <c r="D51">
+        <v>1959</v>
+      </c>
+      <c r="M51" t="s">
+        <v>79</v>
+      </c>
+      <c r="N51" t="s">
+        <v>123</v>
+      </c>
+      <c r="P51" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>732</v>
+      </c>
+      <c r="B52" t="s">
+        <v>727</v>
+      </c>
+      <c r="C52" t="s">
+        <v>703</v>
+      </c>
+      <c r="D52">
+        <v>1959</v>
+      </c>
+      <c r="F52" t="s">
+        <v>51</v>
+      </c>
+      <c r="I52" t="s">
+        <v>704</v>
+      </c>
+      <c r="M52" t="s">
+        <v>79</v>
+      </c>
+      <c r="N52" t="s">
+        <v>123</v>
+      </c>
+      <c r="P52" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>733</v>
+      </c>
+      <c r="B53" t="s">
+        <v>726</v>
+      </c>
+      <c r="C53" t="s">
+        <v>697</v>
+      </c>
+      <c r="D53">
+        <v>1959</v>
+      </c>
+      <c r="M53" t="s">
+        <v>79</v>
+      </c>
+      <c r="N53" t="s">
+        <v>123</v>
+      </c>
+      <c r="P53" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>734</v>
+      </c>
+      <c r="B54" t="s">
+        <v>728</v>
+      </c>
+      <c r="C54" t="s">
+        <v>699</v>
+      </c>
+      <c r="D54">
+        <v>1959</v>
+      </c>
+      <c r="M54" t="s">
+        <v>79</v>
+      </c>
+      <c r="N54" t="s">
+        <v>123</v>
+      </c>
+      <c r="P54" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>735</v>
+      </c>
+      <c r="B55" t="s">
+        <v>725</v>
+      </c>
+      <c r="C55" t="s">
+        <v>698</v>
+      </c>
+      <c r="D55">
+        <v>1959</v>
+      </c>
+      <c r="M55" t="s">
+        <v>79</v>
+      </c>
+      <c r="N55" t="s">
+        <v>123</v>
+      </c>
+      <c r="P55" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>736</v>
+      </c>
+      <c r="B56" t="s">
+        <v>701</v>
+      </c>
+      <c r="C56" t="s">
+        <v>702</v>
+      </c>
+      <c r="D56">
+        <v>1986</v>
+      </c>
+      <c r="M56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>737</v>
+      </c>
+      <c r="B57" t="s">
+        <v>707</v>
+      </c>
+      <c r="C57" t="s">
+        <v>706</v>
+      </c>
+      <c r="D57">
+        <v>1996</v>
+      </c>
+      <c r="E57" t="s">
+        <v>720</v>
+      </c>
+      <c r="G57" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s">
+        <v>708</v>
+      </c>
+      <c r="J57" t="s">
+        <v>709</v>
+      </c>
+      <c r="K57" t="s">
+        <v>710</v>
+      </c>
+      <c r="L57" t="s">
+        <v>721</v>
+      </c>
+      <c r="M57" t="s">
+        <v>79</v>
+      </c>
+      <c r="N57" t="s">
+        <v>584</v>
+      </c>
+      <c r="P57" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>987</v>
+      </c>
+      <c r="B58" t="s">
+        <v>887</v>
+      </c>
+      <c r="C58" t="s">
+        <v>738</v>
+      </c>
+      <c r="D58">
+        <v>1954</v>
+      </c>
+      <c r="F58" t="s">
+        <v>51</v>
+      </c>
+      <c r="I58" t="s">
+        <v>748</v>
+      </c>
+      <c r="M58" t="s">
+        <v>79</v>
+      </c>
+      <c r="N58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>988</v>
+      </c>
+      <c r="B59" t="s">
+        <v>888</v>
+      </c>
+      <c r="C59" t="s">
+        <v>739</v>
+      </c>
+      <c r="D59">
+        <v>1955</v>
+      </c>
+      <c r="F59" t="s">
+        <v>51</v>
+      </c>
+      <c r="M59" t="s">
+        <v>79</v>
+      </c>
+      <c r="N59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>989</v>
+      </c>
+      <c r="B60" t="s">
+        <v>889</v>
+      </c>
+      <c r="C60" t="s">
+        <v>740</v>
+      </c>
+      <c r="D60">
+        <v>1955</v>
+      </c>
+      <c r="F60" t="s">
+        <v>51</v>
+      </c>
+      <c r="M60" t="s">
+        <v>79</v>
+      </c>
+      <c r="N60" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>990</v>
+      </c>
+      <c r="B61" t="s">
+        <v>890</v>
+      </c>
+      <c r="C61" t="s">
+        <v>741</v>
+      </c>
+      <c r="D61">
+        <v>1956</v>
+      </c>
+      <c r="F61" t="s">
+        <v>51</v>
+      </c>
+      <c r="M61" t="s">
+        <v>79</v>
+      </c>
+      <c r="N61" t="s">
+        <v>123</v>
+      </c>
+      <c r="P61" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>991</v>
+      </c>
+      <c r="B62" t="s">
+        <v>891</v>
+      </c>
+      <c r="C62" t="s">
+        <v>742</v>
+      </c>
+      <c r="D62">
+        <v>1976</v>
+      </c>
+      <c r="F62" t="s">
+        <v>51</v>
+      </c>
+      <c r="I62" t="s">
+        <v>743</v>
+      </c>
+      <c r="M62" t="s">
+        <v>79</v>
+      </c>
+      <c r="N62" t="s">
+        <v>123</v>
+      </c>
+      <c r="P62" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>992</v>
+      </c>
+      <c r="B63" t="s">
+        <v>892</v>
+      </c>
+      <c r="C63" t="s">
+        <v>745</v>
+      </c>
+      <c r="D63">
+        <v>1960</v>
+      </c>
+      <c r="F63" t="s">
+        <v>51</v>
+      </c>
+      <c r="I63" t="s">
+        <v>746</v>
+      </c>
+      <c r="M63" t="s">
+        <v>79</v>
+      </c>
+      <c r="N63" t="s">
+        <v>123</v>
+      </c>
+      <c r="P63" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>993</v>
+      </c>
+      <c r="B64" t="s">
+        <v>893</v>
+      </c>
+      <c r="C64" t="s">
+        <v>750</v>
+      </c>
+      <c r="D64">
+        <v>1989</v>
+      </c>
+      <c r="F64" t="s">
+        <v>51</v>
+      </c>
+      <c r="M64" t="s">
+        <v>79</v>
+      </c>
+      <c r="P64" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>994</v>
+      </c>
+      <c r="B65" t="s">
+        <v>894</v>
+      </c>
+      <c r="C65" t="s">
+        <v>751</v>
+      </c>
+      <c r="D65">
+        <v>1964</v>
+      </c>
+      <c r="M65" t="s">
+        <v>79</v>
+      </c>
+      <c r="P65" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>995</v>
+      </c>
+      <c r="B66" t="s">
+        <v>752</v>
+      </c>
+      <c r="C66" t="s">
+        <v>753</v>
+      </c>
+      <c r="D66">
+        <v>2010</v>
+      </c>
+      <c r="M66" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>996</v>
+      </c>
+      <c r="B67" t="s">
+        <v>756</v>
+      </c>
+      <c r="C67" t="s">
+        <v>754</v>
+      </c>
+      <c r="D67">
+        <v>2025</v>
+      </c>
+      <c r="E67" t="s">
+        <v>755</v>
+      </c>
+      <c r="F67" t="s">
+        <v>38</v>
+      </c>
+      <c r="G67" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s">
+        <v>757</v>
+      </c>
+      <c r="J67" t="s">
+        <v>758</v>
+      </c>
+      <c r="K67" t="s">
+        <v>759</v>
+      </c>
+      <c r="L67" t="s">
+        <v>760</v>
+      </c>
+      <c r="M67" t="s">
+        <v>79</v>
+      </c>
+      <c r="N67" t="s">
+        <v>123</v>
+      </c>
+      <c r="P67" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>997</v>
+      </c>
+      <c r="B68" t="s">
+        <v>764</v>
+      </c>
+      <c r="C68" t="s">
+        <v>763</v>
+      </c>
+      <c r="D68">
+        <v>2019</v>
+      </c>
+      <c r="E68" t="s">
+        <v>127</v>
+      </c>
+      <c r="F68" t="s">
+        <v>38</v>
+      </c>
+      <c r="G68" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s">
+        <v>765</v>
+      </c>
+      <c r="J68" t="s">
+        <v>767</v>
+      </c>
+      <c r="K68" t="s">
+        <v>768</v>
+      </c>
+      <c r="L68" t="s">
+        <v>769</v>
+      </c>
+      <c r="M68" t="s">
+        <v>79</v>
+      </c>
+      <c r="N68" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>998</v>
+      </c>
+      <c r="B69" t="s">
+        <v>788</v>
+      </c>
+      <c r="C69" t="s">
+        <v>787</v>
+      </c>
+      <c r="D69">
+        <v>2022</v>
+      </c>
+      <c r="E69" t="s">
+        <v>600</v>
+      </c>
+      <c r="F69" t="s">
+        <v>38</v>
+      </c>
+      <c r="M69" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>999</v>
+      </c>
+      <c r="B70" t="s">
+        <v>790</v>
+      </c>
+      <c r="C70" t="s">
+        <v>789</v>
+      </c>
+      <c r="D70">
+        <v>2025</v>
+      </c>
+      <c r="E70" t="s">
+        <v>791</v>
+      </c>
+      <c r="F70" t="s">
+        <v>38</v>
+      </c>
+      <c r="M70" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B71" t="s">
+        <v>792</v>
+      </c>
+      <c r="C71" t="s">
+        <v>793</v>
+      </c>
+      <c r="D71">
+        <v>2015</v>
+      </c>
+      <c r="E71" t="s">
+        <v>351</v>
+      </c>
+      <c r="M71" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B72" t="s">
+        <v>795</v>
+      </c>
+      <c r="C72" t="s">
+        <v>794</v>
+      </c>
+      <c r="D72">
+        <v>2023</v>
+      </c>
+      <c r="E72" t="s">
+        <v>351</v>
+      </c>
+      <c r="M72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B73" t="s">
+        <v>895</v>
+      </c>
+      <c r="C73" t="s">
+        <v>796</v>
+      </c>
+      <c r="M73" t="s">
+        <v>79</v>
+      </c>
+      <c r="N73" t="s">
+        <v>123</v>
+      </c>
+      <c r="P73" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B74" t="s">
+        <v>896</v>
+      </c>
+      <c r="C74" t="s">
+        <v>797</v>
+      </c>
+      <c r="M74" t="s">
+        <v>79</v>
+      </c>
+      <c r="P74" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B75" t="s">
+        <v>897</v>
+      </c>
+      <c r="C75" t="s">
+        <v>798</v>
+      </c>
+      <c r="D75">
+        <v>1959</v>
+      </c>
+      <c r="E75" t="s">
+        <v>438</v>
+      </c>
+      <c r="I75" t="s">
+        <v>799</v>
+      </c>
+      <c r="J75" t="s">
+        <v>800</v>
+      </c>
+      <c r="K75" t="s">
+        <v>813</v>
+      </c>
+      <c r="M75" t="s">
+        <v>79</v>
+      </c>
+      <c r="P75" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B76" t="s">
+        <v>815</v>
+      </c>
+      <c r="C76" t="s">
+        <v>814</v>
+      </c>
+      <c r="D76">
+        <v>2019</v>
+      </c>
+      <c r="E76" t="s">
+        <v>816</v>
+      </c>
+      <c r="F76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G76" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s">
+        <v>817</v>
+      </c>
+      <c r="J76" t="s">
+        <v>817</v>
+      </c>
+      <c r="M76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B77" t="s">
+        <v>898</v>
+      </c>
+      <c r="C77" t="s">
+        <v>818</v>
+      </c>
+      <c r="D77">
+        <v>1965</v>
+      </c>
+      <c r="F77" t="s">
+        <v>51</v>
+      </c>
+      <c r="I77" t="s">
+        <v>819</v>
+      </c>
+      <c r="M77" t="s">
+        <v>79</v>
+      </c>
+      <c r="P77" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B78" t="s">
+        <v>899</v>
+      </c>
+      <c r="C78" t="s">
+        <v>821</v>
+      </c>
+      <c r="D78">
+        <v>1975</v>
+      </c>
+      <c r="F78" t="s">
+        <v>51</v>
+      </c>
+      <c r="M78" t="s">
+        <v>79</v>
+      </c>
+      <c r="P78" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B79" t="s">
+        <v>900</v>
+      </c>
+      <c r="C79" t="s">
+        <v>822</v>
+      </c>
+      <c r="F79" t="s">
+        <v>51</v>
+      </c>
+      <c r="M79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B80" t="s">
+        <v>901</v>
+      </c>
+      <c r="C80" t="s">
+        <v>823</v>
+      </c>
+      <c r="D80">
+        <v>1960</v>
+      </c>
+      <c r="E80" t="s">
+        <v>824</v>
+      </c>
+      <c r="F80" t="s">
+        <v>51</v>
+      </c>
+      <c r="I80" t="s">
+        <v>743</v>
+      </c>
+      <c r="K80" t="s">
+        <v>825</v>
+      </c>
+      <c r="M80" t="s">
+        <v>79</v>
+      </c>
+      <c r="P80" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B81" t="s">
+        <v>902</v>
+      </c>
+      <c r="C81" t="s">
+        <v>830</v>
+      </c>
+      <c r="D81">
+        <v>1956</v>
+      </c>
+      <c r="F81" t="s">
+        <v>51</v>
+      </c>
+      <c r="I81" t="s">
+        <v>831</v>
+      </c>
+      <c r="M81" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B82" t="s">
+        <v>903</v>
+      </c>
+      <c r="C82" t="s">
+        <v>833</v>
+      </c>
+      <c r="F82" t="s">
+        <v>51</v>
+      </c>
+      <c r="M82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B83" t="s">
+        <v>837</v>
+      </c>
+      <c r="C83" t="s">
+        <v>834</v>
+      </c>
+      <c r="D83">
+        <v>1970</v>
+      </c>
+      <c r="F83" t="s">
+        <v>51</v>
+      </c>
+      <c r="M83" t="s">
+        <v>79</v>
+      </c>
+      <c r="P83" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B84" t="s">
+        <v>904</v>
+      </c>
+      <c r="C84" t="s">
+        <v>838</v>
+      </c>
+      <c r="D84">
+        <v>1976</v>
+      </c>
+      <c r="F84" t="s">
+        <v>51</v>
+      </c>
+      <c r="M84" t="s">
+        <v>79</v>
+      </c>
+      <c r="P84" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B85" t="s">
+        <v>905</v>
+      </c>
+      <c r="C85" t="s">
+        <v>839</v>
+      </c>
+      <c r="F85" t="s">
+        <v>51</v>
+      </c>
+      <c r="M85" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B86" t="s">
+        <v>906</v>
+      </c>
+      <c r="C86" t="s">
+        <v>840</v>
+      </c>
+      <c r="F86" t="s">
+        <v>51</v>
+      </c>
+      <c r="M86" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B87" t="s">
+        <v>842</v>
+      </c>
+      <c r="C87" t="s">
+        <v>841</v>
+      </c>
+      <c r="D87">
+        <v>2007</v>
+      </c>
+      <c r="F87" t="s">
+        <v>51</v>
+      </c>
+      <c r="M87" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B88" t="s">
+        <v>907</v>
+      </c>
+      <c r="C88" t="s">
+        <v>843</v>
+      </c>
+      <c r="F88" t="s">
+        <v>51</v>
+      </c>
+      <c r="M88" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B89" t="s">
+        <v>908</v>
+      </c>
+      <c r="C89" t="s">
+        <v>844</v>
+      </c>
+      <c r="F89" t="s">
+        <v>51</v>
+      </c>
+      <c r="M89" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B90" t="s">
+        <v>909</v>
+      </c>
+      <c r="C90" t="s">
+        <v>845</v>
+      </c>
+      <c r="F90" t="s">
+        <v>51</v>
+      </c>
+      <c r="M90" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B91" t="s">
+        <v>910</v>
+      </c>
+      <c r="C91" t="s">
+        <v>846</v>
+      </c>
+      <c r="D91">
+        <v>1966</v>
+      </c>
+      <c r="F91" t="s">
+        <v>51</v>
+      </c>
+      <c r="M91" t="s">
+        <v>79</v>
+      </c>
+      <c r="P91" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B92" t="s">
+        <v>911</v>
+      </c>
+      <c r="C92" t="s">
+        <v>847</v>
+      </c>
+      <c r="D92">
+        <v>1963</v>
+      </c>
+      <c r="F92" t="s">
+        <v>51</v>
+      </c>
+      <c r="I92" t="s">
+        <v>848</v>
+      </c>
+      <c r="M92" t="s">
+        <v>79</v>
+      </c>
+      <c r="P92" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B93" t="s">
+        <v>912</v>
+      </c>
+      <c r="C93" t="s">
+        <v>855</v>
+      </c>
+      <c r="F93" t="s">
+        <v>51</v>
+      </c>
+      <c r="M93" t="s">
+        <v>79</v>
+      </c>
+      <c r="P93" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B94" t="s">
+        <v>913</v>
+      </c>
+      <c r="C94" t="s">
+        <v>856</v>
+      </c>
+      <c r="D94">
+        <v>1980</v>
+      </c>
+      <c r="M94" t="s">
+        <v>79</v>
+      </c>
+      <c r="P94" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B95" t="s">
+        <v>860</v>
+      </c>
+      <c r="C95" t="s">
+        <v>859</v>
+      </c>
+      <c r="D95">
+        <v>2014</v>
+      </c>
+      <c r="E95" t="s">
+        <v>755</v>
+      </c>
+      <c r="M95" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B96" t="s">
+        <v>862</v>
+      </c>
+      <c r="C96" t="s">
+        <v>861</v>
+      </c>
+      <c r="D96">
+        <v>1990</v>
+      </c>
+      <c r="E96" t="s">
+        <v>127</v>
+      </c>
+      <c r="M96" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B97" t="s">
+        <v>914</v>
+      </c>
+      <c r="C97" t="s">
+        <v>863</v>
+      </c>
+      <c r="D97">
+        <v>1985</v>
+      </c>
+      <c r="I97" t="s">
+        <v>864</v>
+      </c>
+      <c r="J97" t="s">
+        <v>864</v>
+      </c>
+      <c r="M97" t="s">
+        <v>79</v>
+      </c>
+      <c r="P97" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B98" t="s">
+        <v>915</v>
+      </c>
+      <c r="C98" t="s">
+        <v>866</v>
+      </c>
+      <c r="D98">
+        <v>1974</v>
+      </c>
+      <c r="F98" t="s">
+        <v>51</v>
+      </c>
+      <c r="L98" t="s">
+        <v>868</v>
+      </c>
+      <c r="M98" t="s">
+        <v>79</v>
+      </c>
+      <c r="P98" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B99" t="s">
+        <v>916</v>
+      </c>
+      <c r="C99" t="s">
+        <v>867</v>
+      </c>
+      <c r="D99">
+        <v>2014</v>
+      </c>
+      <c r="F99" t="s">
+        <v>38</v>
+      </c>
+      <c r="M99" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B100" t="s">
+        <v>917</v>
+      </c>
+      <c r="C100" t="s">
+        <v>869</v>
+      </c>
+      <c r="D100">
+        <v>1978</v>
+      </c>
+      <c r="E100" t="s">
+        <v>870</v>
+      </c>
+      <c r="F100" t="s">
+        <v>51</v>
+      </c>
+      <c r="I100" t="s">
+        <v>871</v>
+      </c>
+      <c r="J100" t="s">
+        <v>871</v>
+      </c>
+      <c r="M100" t="s">
+        <v>79</v>
+      </c>
+      <c r="N100" t="s">
+        <v>123</v>
+      </c>
+      <c r="P100" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B101" t="s">
+        <v>975</v>
+      </c>
+      <c r="C101" t="s">
+        <v>873</v>
+      </c>
+      <c r="D101">
+        <v>1965</v>
+      </c>
+      <c r="F101" t="s">
+        <v>51</v>
+      </c>
+      <c r="I101" t="s">
+        <v>918</v>
+      </c>
+      <c r="M101" t="s">
+        <v>79</v>
+      </c>
+      <c r="N101" t="s">
+        <v>123</v>
+      </c>
+      <c r="P101" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B102" t="s">
+        <v>976</v>
+      </c>
+      <c r="C102" t="s">
+        <v>874</v>
+      </c>
+      <c r="F102" t="s">
+        <v>51</v>
+      </c>
+      <c r="M102" t="s">
+        <v>79</v>
+      </c>
+      <c r="N102" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B103" t="s">
+        <v>977</v>
+      </c>
+      <c r="C103" t="s">
+        <v>875</v>
+      </c>
+      <c r="D103">
+        <v>1982</v>
+      </c>
+      <c r="F103" t="s">
+        <v>51</v>
+      </c>
+      <c r="I103" t="s">
+        <v>925</v>
+      </c>
+      <c r="M103" t="s">
+        <v>79</v>
+      </c>
+      <c r="N103" t="s">
+        <v>123</v>
+      </c>
+      <c r="P103" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B104" t="s">
+        <v>978</v>
+      </c>
+      <c r="C104" t="s">
+        <v>876</v>
+      </c>
+      <c r="D104">
+        <v>1985</v>
+      </c>
+      <c r="F104" t="s">
+        <v>51</v>
+      </c>
+      <c r="M104" t="s">
+        <v>79</v>
+      </c>
+      <c r="N104" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B105" t="s">
+        <v>979</v>
+      </c>
+      <c r="C105" t="s">
+        <v>877</v>
+      </c>
+      <c r="F105" t="s">
+        <v>51</v>
+      </c>
+      <c r="M105" t="s">
+        <v>79</v>
+      </c>
+      <c r="N105" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B106" t="s">
+        <v>980</v>
+      </c>
+      <c r="C106" t="s">
+        <v>878</v>
+      </c>
+      <c r="F106" t="s">
+        <v>51</v>
+      </c>
+      <c r="M106" t="s">
+        <v>79</v>
+      </c>
+      <c r="N106" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B107" t="s">
+        <v>981</v>
+      </c>
+      <c r="C107" t="s">
+        <v>879</v>
+      </c>
+      <c r="F107" t="s">
+        <v>51</v>
+      </c>
+      <c r="M107" t="s">
+        <v>79</v>
+      </c>
+      <c r="N107" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B108" t="s">
+        <v>982</v>
+      </c>
+      <c r="C108" t="s">
+        <v>880</v>
+      </c>
+      <c r="F108" t="s">
+        <v>51</v>
+      </c>
+      <c r="M108" t="s">
+        <v>79</v>
+      </c>
+      <c r="N108" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B109" t="s">
+        <v>983</v>
+      </c>
+      <c r="C109" t="s">
+        <v>881</v>
+      </c>
+      <c r="F109" t="s">
+        <v>51</v>
+      </c>
+      <c r="M109" t="s">
+        <v>79</v>
+      </c>
+      <c r="N109" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B110" t="s">
+        <v>984</v>
+      </c>
+      <c r="C110" t="s">
+        <v>882</v>
+      </c>
+      <c r="D110">
+        <v>1984</v>
+      </c>
+      <c r="F110" t="s">
+        <v>51</v>
+      </c>
+      <c r="I110" t="s">
+        <v>918</v>
+      </c>
+      <c r="M110" t="s">
+        <v>79</v>
+      </c>
+      <c r="N110" t="s">
+        <v>123</v>
+      </c>
+      <c r="P110" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B111" t="s">
+        <v>985</v>
+      </c>
+      <c r="C111" t="s">
+        <v>883</v>
+      </c>
+      <c r="D111">
+        <v>1983</v>
+      </c>
+      <c r="E111" t="s">
+        <v>941</v>
+      </c>
+      <c r="F111" t="s">
+        <v>51</v>
+      </c>
+      <c r="I111" t="s">
+        <v>831</v>
+      </c>
+      <c r="M111" t="s">
+        <v>79</v>
+      </c>
+      <c r="N111" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B112" t="s">
+        <v>986</v>
+      </c>
+      <c r="C112" t="s">
+        <v>953</v>
+      </c>
+      <c r="F112" t="s">
+        <v>51</v>
+      </c>
+      <c r="M112" t="s">
+        <v>79</v>
+      </c>
+      <c r="N112" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B113" t="s">
+        <v>964</v>
+      </c>
+      <c r="C113" t="s">
+        <v>962</v>
+      </c>
+      <c r="D113">
+        <v>1980</v>
+      </c>
+      <c r="E113" t="s">
+        <v>963</v>
+      </c>
+      <c r="F113" t="s">
+        <v>51</v>
+      </c>
+      <c r="M113" t="s">
+        <v>79</v>
+      </c>
+      <c r="N113" t="s">
+        <v>123</v>
+      </c>
+      <c r="P113" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B114" t="s">
+        <v>973</v>
+      </c>
+      <c r="C114" t="s">
+        <v>884</v>
+      </c>
+      <c r="D114">
+        <v>1985</v>
+      </c>
+      <c r="F114" t="s">
+        <v>51</v>
+      </c>
+      <c r="I114" t="s">
+        <v>925</v>
+      </c>
+      <c r="M114" t="s">
+        <v>79</v>
+      </c>
+      <c r="N114" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B115" t="s">
+        <v>974</v>
+      </c>
+      <c r="C115" t="s">
+        <v>885</v>
+      </c>
+      <c r="F115" t="s">
+        <v>51</v>
+      </c>
+      <c r="M115" t="s">
+        <v>79</v>
+      </c>
+      <c r="N115" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B116" t="s">
+        <v>970</v>
+      </c>
+      <c r="C116" t="s">
+        <v>886</v>
+      </c>
+      <c r="F116" t="s">
+        <v>51</v>
+      </c>
+      <c r="M116" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B117" t="s">
+        <v>921</v>
+      </c>
+      <c r="C117" t="s">
+        <v>920</v>
+      </c>
+      <c r="D117">
+        <v>2015</v>
+      </c>
+      <c r="E117" t="s">
+        <v>922</v>
+      </c>
+      <c r="F117" t="s">
+        <v>51</v>
+      </c>
+      <c r="I117" t="s">
+        <v>923</v>
+      </c>
+      <c r="M117" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B118" t="s">
+        <v>933</v>
+      </c>
+      <c r="C118" t="s">
+        <v>931</v>
+      </c>
+      <c r="D118">
+        <v>2019</v>
+      </c>
+      <c r="E118" t="s">
+        <v>932</v>
+      </c>
+      <c r="F118" t="s">
+        <v>38</v>
+      </c>
+      <c r="M118" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B119" t="s">
+        <v>934</v>
+      </c>
+      <c r="D119">
+        <v>2013</v>
+      </c>
+      <c r="F119" t="s">
+        <v>51</v>
+      </c>
+      <c r="I119" t="s">
+        <v>935</v>
+      </c>
+      <c r="M119" t="s">
+        <v>53</v>
+      </c>
+      <c r="N119" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B120" t="s">
+        <v>937</v>
+      </c>
+      <c r="C120" t="s">
+        <v>936</v>
+      </c>
+      <c r="D120">
+        <v>2022</v>
+      </c>
+      <c r="F120" t="s">
+        <v>51</v>
+      </c>
+      <c r="M120" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B121" t="s">
+        <v>938</v>
+      </c>
+      <c r="D121">
+        <v>2015</v>
+      </c>
+      <c r="E121" t="s">
+        <v>939</v>
+      </c>
+      <c r="F121" t="s">
+        <v>38</v>
+      </c>
+      <c r="M121" t="s">
+        <v>94</v>
+      </c>
+      <c r="N121" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B122" t="s">
+        <v>972</v>
+      </c>
+      <c r="C122" t="s">
+        <v>940</v>
+      </c>
+      <c r="D122">
+        <v>1955</v>
+      </c>
+      <c r="E122" t="s">
+        <v>941</v>
+      </c>
+      <c r="F122" t="s">
+        <v>51</v>
+      </c>
+      <c r="I122" t="s">
+        <v>942</v>
+      </c>
+      <c r="M122" t="s">
+        <v>79</v>
+      </c>
+      <c r="N122" t="s">
+        <v>123</v>
+      </c>
+      <c r="P122" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B123" t="s">
+        <v>946</v>
+      </c>
+      <c r="C123" t="s">
+        <v>945</v>
+      </c>
+      <c r="D123">
+        <v>2018</v>
+      </c>
+      <c r="E123" t="s">
+        <v>949</v>
+      </c>
+      <c r="F123" t="s">
+        <v>38</v>
+      </c>
+      <c r="M123" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B124" t="s">
+        <v>948</v>
+      </c>
+      <c r="C124" t="s">
+        <v>947</v>
+      </c>
+      <c r="D124">
+        <v>2007</v>
+      </c>
+      <c r="E124" t="s">
+        <v>950</v>
+      </c>
+      <c r="F124" t="s">
+        <v>38</v>
+      </c>
+      <c r="M124" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B125" t="s">
+        <v>951</v>
+      </c>
+      <c r="D125">
+        <v>2010</v>
+      </c>
+      <c r="E125" t="s">
+        <v>533</v>
+      </c>
+      <c r="F125" t="s">
+        <v>38</v>
+      </c>
+      <c r="I125" t="s">
+        <v>952</v>
+      </c>
+      <c r="M125" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B126" t="s">
+        <v>956</v>
+      </c>
+      <c r="C126" t="s">
+        <v>954</v>
+      </c>
+      <c r="D126">
+        <v>1988</v>
+      </c>
+      <c r="E126" t="s">
+        <v>955</v>
+      </c>
+      <c r="F126" t="s">
+        <v>51</v>
+      </c>
+      <c r="I126" t="s">
+        <v>957</v>
+      </c>
+      <c r="M126" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B127" t="s">
+        <v>971</v>
+      </c>
+      <c r="C127" t="s">
+        <v>965</v>
+      </c>
+      <c r="D127">
+        <v>2014</v>
+      </c>
+      <c r="F127" t="s">
+        <v>38</v>
+      </c>
+      <c r="I127" t="s">
+        <v>966</v>
+      </c>
+      <c r="J127" t="s">
+        <v>967</v>
+      </c>
+      <c r="M127" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D128">
+        <v>2011</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F128" t="s">
+        <v>38</v>
+      </c>
+      <c r="M128" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D129">
+        <v>2010</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F129" t="s">
+        <v>38</v>
+      </c>
+      <c r="M129" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D130">
+        <v>1939</v>
+      </c>
+      <c r="F130" t="s">
+        <v>51</v>
+      </c>
+      <c r="I130" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M130" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D131">
+        <v>1939</v>
+      </c>
+      <c r="F131" t="s">
+        <v>51</v>
+      </c>
+      <c r="I131" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M131" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D132">
+        <v>1939</v>
+      </c>
+      <c r="F132" t="s">
+        <v>51</v>
+      </c>
+      <c r="I132" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M132" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D133">
+        <v>1939</v>
+      </c>
+      <c r="F133" t="s">
+        <v>51</v>
+      </c>
+      <c r="I133" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M133" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D134">
+        <v>1939</v>
+      </c>
+      <c r="F134" t="s">
+        <v>51</v>
+      </c>
+      <c r="I134" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M134" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D135">
+        <v>1955</v>
+      </c>
+      <c r="F135" t="s">
+        <v>38</v>
+      </c>
+      <c r="M135" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D136">
+        <v>1953</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F136" t="s">
+        <v>38</v>
+      </c>
+      <c r="I136" t="s">
+        <v>1126</v>
+      </c>
+      <c r="M136" t="s">
+        <v>79</v>
+      </c>
+      <c r="P136" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F137" t="s">
+        <v>51</v>
+      </c>
+      <c r="M137" t="s">
+        <v>79</v>
+      </c>
+      <c r="P137" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F138" t="s">
+        <v>51</v>
+      </c>
+      <c r="M138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F139" t="s">
+        <v>51</v>
+      </c>
+      <c r="M139" t="s">
+        <v>79</v>
+      </c>
+      <c r="P139" t="s">
         <v>420</v>
       </c>
     </row>
@@ -4625,7 +8137,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
@@ -5989,7 +9501,7 @@
         <v>194</v>
       </c>
       <c r="G50" t="s">
-        <v>385</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -6096,7 +9608,7 @@
         <v>462</v>
       </c>
       <c r="D57" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E57">
         <v>1912</v>
@@ -6333,7 +9845,7 @@
         <v>560</v>
       </c>
       <c r="B75" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C75" t="s">
         <v>544</v>
@@ -6350,7 +9862,7 @@
         <v>561</v>
       </c>
       <c r="B76" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C76" t="s">
         <v>545</v>
@@ -6367,7 +9879,7 @@
         <v>562</v>
       </c>
       <c r="B77" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C77" t="s">
         <v>546</v>
@@ -6398,13 +9910,13 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B79" t="s">
         <v>566</v>
       </c>
       <c r="C79" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D79" t="s">
         <v>23</v>
@@ -6412,13 +9924,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B80" t="s">
         <v>567</v>
       </c>
       <c r="C80" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
@@ -6426,13 +9938,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B81" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C81" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D81" t="s">
         <v>190</v>
@@ -6443,13 +9955,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B82" t="s">
-        <v>570</v>
+        <v>927</v>
       </c>
       <c r="C82" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D82" t="s">
         <v>190</v>
@@ -6466,13 +9978,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B83" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C83" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D83" t="s">
         <v>190</v>
@@ -6483,13 +9995,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B84" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C84" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D84" t="s">
         <v>190</v>
@@ -6500,13 +10012,13 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B85" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C85" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D85" t="s">
         <v>190</v>
@@ -6517,13 +10029,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B86" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C86" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D86" t="s">
         <v>23</v>
@@ -6531,13 +10043,13 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B87" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C87" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D87" t="s">
         <v>24</v>
@@ -6545,13 +10057,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B88" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C88" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D88" t="s">
         <v>190</v>
@@ -6568,13 +10080,13 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B89" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C89" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D89" t="s">
         <v>190</v>
@@ -6585,13 +10097,13 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B90" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C90" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D90" t="s">
         <v>190</v>
@@ -6602,13 +10114,13 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B91" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C91" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D91" t="s">
         <v>194</v>
@@ -6616,10 +10128,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B92" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D92" t="s">
         <v>190</v>
@@ -6627,10 +10139,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="B93" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D93" t="s">
         <v>190</v>
@@ -6638,13 +10150,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B94" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C94" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D94" t="s">
         <v>23</v>
@@ -6652,13 +10164,13 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B95" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C95" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D95" t="s">
         <v>24</v>
@@ -6666,13 +10178,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B96" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C96" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D96" t="s">
         <v>190</v>
@@ -6680,13 +10192,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B97" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C97" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D97" t="s">
         <v>190</v>
@@ -6694,13 +10206,13 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B98" t="s">
+        <v>618</v>
+      </c>
+      <c r="C98" t="s">
         <v>621</v>
-      </c>
-      <c r="C98" t="s">
-        <v>624</v>
       </c>
       <c r="D98" t="s">
         <v>190</v>
@@ -6708,13 +10220,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="B99" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C99" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D99" t="s">
         <v>190</v>
@@ -6722,13 +10234,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B100" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C100" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D100" t="s">
         <v>23</v>
@@ -6745,13 +10257,13 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="B101" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C101" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D101" t="s">
         <v>23</v>
@@ -6759,13 +10271,13 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B102" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C102" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D102" t="s">
         <v>23</v>
@@ -6773,13 +10285,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B103" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C103" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D103" t="s">
         <v>23</v>
@@ -6787,13 +10299,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B104" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C104" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D104" t="s">
         <v>24</v>
@@ -6801,13 +10313,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B105" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C105" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D105" t="s">
         <v>190</v>
@@ -6815,13 +10327,13 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B106" t="s">
+        <v>640</v>
+      </c>
+      <c r="C106" t="s">
         <v>643</v>
-      </c>
-      <c r="C106" t="s">
-        <v>646</v>
       </c>
       <c r="D106" t="s">
         <v>190</v>
@@ -6829,16 +10341,789 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B107" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C107" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D107" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B108" t="s">
+        <v>693</v>
+      </c>
+      <c r="C108" t="s">
+        <v>694</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108">
+        <v>1916</v>
+      </c>
+      <c r="F108">
+        <v>2003</v>
+      </c>
+      <c r="G108" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B109" t="s">
+        <v>704</v>
+      </c>
+      <c r="C109" t="s">
+        <v>705</v>
+      </c>
+      <c r="D109" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B110" t="s">
+        <v>711</v>
+      </c>
+      <c r="C110" t="s">
+        <v>719</v>
+      </c>
+      <c r="D110" t="s">
+        <v>23</v>
+      </c>
+      <c r="G110" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B111" t="s">
+        <v>712</v>
+      </c>
+      <c r="C111" t="s">
+        <v>718</v>
+      </c>
+      <c r="D111" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B112" t="s">
+        <v>709</v>
+      </c>
+      <c r="C112" t="s">
+        <v>717</v>
+      </c>
+      <c r="D112" t="s">
+        <v>24</v>
+      </c>
+      <c r="G112" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B113" t="s">
+        <v>713</v>
+      </c>
+      <c r="C113" t="s">
+        <v>716</v>
+      </c>
+      <c r="D113" t="s">
+        <v>190</v>
+      </c>
+      <c r="G113" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B114" t="s">
+        <v>714</v>
+      </c>
+      <c r="C114" t="s">
+        <v>715</v>
+      </c>
+      <c r="D114" t="s">
+        <v>190</v>
+      </c>
+      <c r="G114" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B115" t="s">
+        <v>743</v>
+      </c>
+      <c r="C115" t="s">
+        <v>744</v>
+      </c>
+      <c r="D115" t="s">
+        <v>23</v>
+      </c>
+      <c r="G115" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B116" t="s">
+        <v>746</v>
+      </c>
+      <c r="C116" t="s">
+        <v>747</v>
+      </c>
+      <c r="D116" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B117" t="s">
+        <v>748</v>
+      </c>
+      <c r="C117" t="s">
+        <v>749</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
+      </c>
+      <c r="G117" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B118" t="s">
+        <v>765</v>
+      </c>
+      <c r="C118" t="s">
+        <v>779</v>
+      </c>
+      <c r="D118" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B119" t="s">
+        <v>766</v>
+      </c>
+      <c r="C119" t="s">
+        <v>778</v>
+      </c>
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+      <c r="G119" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B120" t="s">
+        <v>770</v>
+      </c>
+      <c r="C120" t="s">
+        <v>777</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="G120" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B121" t="s">
+        <v>771</v>
+      </c>
+      <c r="C121" t="s">
+        <v>776</v>
+      </c>
+      <c r="D121" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B122" t="s">
+        <v>775</v>
+      </c>
+      <c r="C122" t="s">
+        <v>774</v>
+      </c>
+      <c r="D122" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B123" t="s">
+        <v>772</v>
+      </c>
+      <c r="C123" t="s">
+        <v>773</v>
+      </c>
+      <c r="D123" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B124" t="s">
+        <v>780</v>
+      </c>
+      <c r="C124" t="s">
+        <v>786</v>
+      </c>
+      <c r="D124" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B125" t="s">
+        <v>758</v>
+      </c>
+      <c r="C125" t="s">
+        <v>785</v>
+      </c>
+      <c r="D125" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B126" t="s">
+        <v>781</v>
+      </c>
+      <c r="C126" t="s">
+        <v>784</v>
+      </c>
+      <c r="D126" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B127" t="s">
+        <v>782</v>
+      </c>
+      <c r="C127" t="s">
+        <v>783</v>
+      </c>
+      <c r="D127" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B128" t="s">
+        <v>799</v>
+      </c>
+      <c r="C128" t="s">
+        <v>812</v>
+      </c>
+      <c r="D128" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B129" t="s">
+        <v>800</v>
+      </c>
+      <c r="C129" t="s">
+        <v>811</v>
+      </c>
+      <c r="D129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B130" t="s">
+        <v>801</v>
+      </c>
+      <c r="C130" t="s">
+        <v>810</v>
+      </c>
+      <c r="D130" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B131" t="s">
+        <v>802</v>
+      </c>
+      <c r="C131" t="s">
+        <v>809</v>
+      </c>
+      <c r="D131" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B132" t="s">
+        <v>803</v>
+      </c>
+      <c r="C132" t="s">
+        <v>808</v>
+      </c>
+      <c r="D132" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B133" t="s">
+        <v>804</v>
+      </c>
+      <c r="C133" t="s">
+        <v>807</v>
+      </c>
+      <c r="D133" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B134" t="s">
+        <v>805</v>
+      </c>
+      <c r="C134" t="s">
+        <v>806</v>
+      </c>
+      <c r="D134" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B135" t="s">
+        <v>817</v>
+      </c>
+      <c r="D135" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B136" t="s">
+        <v>819</v>
+      </c>
+      <c r="C136" t="s">
+        <v>820</v>
+      </c>
+      <c r="D136" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136">
+        <v>1929</v>
+      </c>
+      <c r="F136">
+        <v>1980</v>
+      </c>
+      <c r="G136" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B137" t="s">
+        <v>826</v>
+      </c>
+      <c r="C137" t="s">
+        <v>829</v>
+      </c>
+      <c r="D137" t="s">
+        <v>190</v>
+      </c>
+      <c r="G137" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B138" t="s">
+        <v>827</v>
+      </c>
+      <c r="C138" t="s">
+        <v>828</v>
+      </c>
+      <c r="D138" t="s">
+        <v>190</v>
+      </c>
+      <c r="G138" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B139" t="s">
+        <v>831</v>
+      </c>
+      <c r="C139" t="s">
+        <v>832</v>
+      </c>
+      <c r="D139" t="s">
+        <v>23</v>
+      </c>
+      <c r="G139" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B140" t="s">
+        <v>849</v>
+      </c>
+      <c r="C140" t="s">
+        <v>854</v>
+      </c>
+      <c r="D140" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140">
+        <v>1925</v>
+      </c>
+      <c r="G140" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B141" t="s">
+        <v>850</v>
+      </c>
+      <c r="C141" t="s">
+        <v>853</v>
+      </c>
+      <c r="D141" t="s">
+        <v>23</v>
+      </c>
+      <c r="G141" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B142" t="s">
+        <v>851</v>
+      </c>
+      <c r="C142" t="s">
+        <v>852</v>
+      </c>
+      <c r="D142" t="s">
+        <v>23</v>
+      </c>
+      <c r="G142" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B143" t="s">
+        <v>864</v>
+      </c>
+      <c r="C143" t="s">
+        <v>865</v>
+      </c>
+      <c r="D143" t="s">
+        <v>194</v>
+      </c>
+      <c r="E143">
+        <v>1932</v>
+      </c>
+      <c r="G143" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B144" t="s">
+        <v>871</v>
+      </c>
+      <c r="C144" t="s">
+        <v>872</v>
+      </c>
+      <c r="D144" t="s">
+        <v>194</v>
+      </c>
+      <c r="E144">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B145" t="s">
+        <v>918</v>
+      </c>
+      <c r="C145" t="s">
+        <v>919</v>
+      </c>
+      <c r="D145" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B146" t="s">
+        <v>923</v>
+      </c>
+      <c r="C146" t="s">
+        <v>924</v>
+      </c>
+      <c r="D146" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B147" t="s">
+        <v>925</v>
+      </c>
+      <c r="C147" t="s">
+        <v>926</v>
+      </c>
+      <c r="D147" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B148" t="s">
+        <v>935</v>
+      </c>
+      <c r="D148" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B149" t="s">
+        <v>942</v>
+      </c>
+      <c r="C149" t="s">
+        <v>943</v>
+      </c>
+      <c r="D149" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149">
+        <v>1929</v>
+      </c>
+      <c r="G149" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B150" t="s">
+        <v>951</v>
+      </c>
+      <c r="D150" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B151" t="s">
+        <v>958</v>
+      </c>
+      <c r="C151" t="s">
+        <v>961</v>
+      </c>
+      <c r="D151" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B152" t="s">
+        <v>959</v>
+      </c>
+      <c r="C152" t="s">
+        <v>960</v>
+      </c>
+      <c r="D152" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B153" t="s">
+        <v>966</v>
+      </c>
+      <c r="C153" t="s">
+        <v>969</v>
+      </c>
+      <c r="D153" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B154" t="s">
+        <v>967</v>
+      </c>
+      <c r="C154" t="s">
+        <v>968</v>
+      </c>
+      <c r="D154" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D155" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D156" t="s">
+        <v>23</v>
+      </c>
+      <c r="E156">
+        <v>1917</v>
+      </c>
+      <c r="F156">
+        <v>1999</v>
       </c>
     </row>
   </sheetData>
@@ -6852,7 +11137,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -7352,13 +11637,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B25" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C25" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D25" t="s">
         <v>79</v>
@@ -7366,13 +11651,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B26" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C26" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -7383,13 +11668,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B27" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C27" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -7397,24 +11682,100 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="B28" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C28" t="s">
-        <v>613</v>
+        <v>610</v>
+      </c>
+      <c r="D28" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B29" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C29" t="s">
-        <v>629</v>
+        <v>626</v>
+      </c>
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B30" t="s">
+        <v>723</v>
+      </c>
+      <c r="C30" t="s">
+        <v>724</v>
+      </c>
+      <c r="D30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>761</v>
+      </c>
+      <c r="C31" t="s">
+        <v>762</v>
+      </c>
+      <c r="D31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B32" t="s">
+        <v>835</v>
+      </c>
+      <c r="C32" t="s">
+        <v>836</v>
+      </c>
+      <c r="D32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="C33" t="s">
+        <v>858</v>
+      </c>
+      <c r="D33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D34" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/tibetan-film.xlsx
+++ b/data/tibetan-film.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skyeju/Desktop/Digital Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A95821-7493-B94D-91CF-9E28C03B1C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3CBF4C-8DEE-A14D-8C5D-6B3402320A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32000" yWindow="-8280" windowWidth="34200" windowHeight="19680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -1833,9 +1833,6 @@
     <t>Pema Tseden</t>
   </si>
   <si>
-    <t>Jinpa;Tseten Tashi;Lobsang Choepel</t>
-  </si>
-  <si>
     <t>万玛才旦</t>
   </si>
   <si>
@@ -3496,6 +3493,9 @@
   </si>
   <si>
     <t>ORG-0033</t>
+  </si>
+  <si>
+    <t>Jinpa;Tseten Tashi;Losang Choepel</t>
   </si>
 </sst>
 </file>
@@ -5191,7 +5191,7 @@
         <v>51</v>
       </c>
       <c r="I23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M23" t="s">
         <v>79</v>
@@ -5666,7 +5666,7 @@
         <v>510</v>
       </c>
       <c r="B40" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C40" t="s">
         <v>503</v>
@@ -5690,7 +5690,7 @@
         <v>567</v>
       </c>
       <c r="K40" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M40" t="s">
         <v>79</v>
@@ -5725,13 +5725,13 @@
         <v>21</v>
       </c>
       <c r="I41" t="s">
+        <v>612</v>
+      </c>
+      <c r="J41" t="s">
         <v>613</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>614</v>
-      </c>
-      <c r="K41" t="s">
-        <v>615</v>
       </c>
       <c r="M41" t="s">
         <v>79</v>
@@ -5740,7 +5740,7 @@
         <v>123</v>
       </c>
       <c r="P41" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
@@ -5748,7 +5748,7 @@
         <v>512</v>
       </c>
       <c r="B42" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C42" t="s">
         <v>505</v>
@@ -5757,7 +5757,7 @@
         <v>1988</v>
       </c>
       <c r="E42" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F42" t="s">
         <v>38</v>
@@ -5766,13 +5766,13 @@
         <v>21</v>
       </c>
       <c r="I42" t="s">
+        <v>648</v>
+      </c>
+      <c r="J42" t="s">
         <v>649</v>
       </c>
-      <c r="J42" t="s">
-        <v>650</v>
-      </c>
       <c r="K42" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="M42" t="s">
         <v>79</v>
@@ -5786,7 +5786,7 @@
         <v>513</v>
       </c>
       <c r="B43" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C43" t="s">
         <v>506</v>
@@ -5812,7 +5812,7 @@
         <v>514</v>
       </c>
       <c r="B44" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C44" t="s">
         <v>507</v>
@@ -5833,7 +5833,7 @@
         <v>583</v>
       </c>
       <c r="K44" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="M44" t="s">
         <v>79</v>
@@ -5850,7 +5850,7 @@
         <v>515</v>
       </c>
       <c r="B45" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C45" t="s">
         <v>508</v>
@@ -5859,7 +5859,7 @@
         <v>1996</v>
       </c>
       <c r="E45" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F45" t="s">
         <v>38</v>
@@ -5876,7 +5876,7 @@
         <v>516</v>
       </c>
       <c r="B46" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C46" t="s">
         <v>509</v>
@@ -5943,13 +5943,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B48" t="s">
         <v>599</v>
       </c>
       <c r="C48" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D48">
         <v>2023</v>
@@ -5970,10 +5970,10 @@
         <v>601</v>
       </c>
       <c r="K48" t="s">
-        <v>602</v>
+        <v>1156</v>
       </c>
       <c r="L48" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="M48" t="s">
         <v>79</v>
@@ -5982,18 +5982,18 @@
         <v>584</v>
       </c>
       <c r="P48" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B49" t="s">
+        <v>627</v>
+      </c>
+      <c r="C49" t="s">
         <v>628</v>
-      </c>
-      <c r="C49" t="s">
-        <v>629</v>
       </c>
       <c r="D49">
         <v>1956</v>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B50" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C50" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D50">
         <v>1959</v>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B51" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C51" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D51">
         <v>1959</v>
@@ -6053,13 +6053,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B52" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C52" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D52">
         <v>1959</v>
@@ -6068,7 +6068,7 @@
         <v>51</v>
       </c>
       <c r="I52" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="M52" t="s">
         <v>79</v>
@@ -6082,13 +6082,13 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B53" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C53" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D53">
         <v>1959</v>
@@ -6105,13 +6105,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B54" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C54" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D54">
         <v>1959</v>
@@ -6128,13 +6128,13 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B55" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C55" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D55">
         <v>1959</v>
@@ -6151,13 +6151,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B56" t="s">
+        <v>700</v>
+      </c>
+      <c r="C56" t="s">
         <v>701</v>
-      </c>
-      <c r="C56" t="s">
-        <v>702</v>
       </c>
       <c r="D56">
         <v>1986</v>
@@ -6168,34 +6168,34 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B57" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C57" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D57">
         <v>1996</v>
       </c>
       <c r="E57" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G57" t="s">
         <v>21</v>
       </c>
       <c r="I57" t="s">
+        <v>707</v>
+      </c>
+      <c r="J57" t="s">
         <v>708</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>709</v>
       </c>
-      <c r="K57" t="s">
-        <v>710</v>
-      </c>
       <c r="L57" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="M57" t="s">
         <v>79</v>
@@ -6204,18 +6204,18 @@
         <v>584</v>
       </c>
       <c r="P57" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B58" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C58" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D58">
         <v>1954</v>
@@ -6224,7 +6224,7 @@
         <v>51</v>
       </c>
       <c r="I58" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="M58" t="s">
         <v>79</v>
@@ -6235,13 +6235,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B59" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C59" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D59">
         <v>1955</v>
@@ -6258,13 +6258,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B60" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C60" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D60">
         <v>1955</v>
@@ -6281,13 +6281,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B61" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C61" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D61">
         <v>1956</v>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B62" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C62" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D62">
         <v>1976</v>
@@ -6322,7 +6322,7 @@
         <v>51</v>
       </c>
       <c r="I62" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="M62" t="s">
         <v>79</v>
@@ -6336,13 +6336,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B63" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C63" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D63">
         <v>1960</v>
@@ -6351,7 +6351,7 @@
         <v>51</v>
       </c>
       <c r="I63" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M63" t="s">
         <v>79</v>
@@ -6365,13 +6365,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B64" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C64" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D64">
         <v>1989</v>
@@ -6388,13 +6388,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B65" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C65" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D65">
         <v>1964</v>
@@ -6408,13 +6408,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B66" t="s">
+        <v>751</v>
+      </c>
+      <c r="C66" t="s">
         <v>752</v>
-      </c>
-      <c r="C66" t="s">
-        <v>753</v>
       </c>
       <c r="D66">
         <v>2010</v>
@@ -6425,19 +6425,19 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B67" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C67" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D67">
         <v>2025</v>
       </c>
       <c r="E67" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F67" t="s">
         <v>38</v>
@@ -6446,16 +6446,16 @@
         <v>21</v>
       </c>
       <c r="I67" t="s">
+        <v>756</v>
+      </c>
+      <c r="J67" t="s">
         <v>757</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>758</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>759</v>
-      </c>
-      <c r="L67" t="s">
-        <v>760</v>
       </c>
       <c r="M67" t="s">
         <v>79</v>
@@ -6464,18 +6464,18 @@
         <v>123</v>
       </c>
       <c r="P67" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B68" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C68" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D68">
         <v>2019</v>
@@ -6490,16 +6490,16 @@
         <v>21</v>
       </c>
       <c r="I68" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="J68" t="s">
+        <v>766</v>
+      </c>
+      <c r="K68" t="s">
         <v>767</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>768</v>
-      </c>
-      <c r="L68" t="s">
-        <v>769</v>
       </c>
       <c r="M68" t="s">
         <v>79</v>
@@ -6510,13 +6510,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B69" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C69" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D69">
         <v>2022</v>
@@ -6533,19 +6533,19 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B70" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C70" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D70">
         <v>2025</v>
       </c>
       <c r="E70" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F70" t="s">
         <v>38</v>
@@ -6556,13 +6556,13 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B71" t="s">
+        <v>791</v>
+      </c>
+      <c r="C71" t="s">
         <v>792</v>
-      </c>
-      <c r="C71" t="s">
-        <v>793</v>
       </c>
       <c r="D71">
         <v>2015</v>
@@ -6576,13 +6576,13 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B72" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C72" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D72">
         <v>2023</v>
@@ -6596,13 +6596,13 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B73" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C73" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M73" t="s">
         <v>79</v>
@@ -6616,13 +6616,13 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B74" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C74" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M74" t="s">
         <v>79</v>
@@ -6633,13 +6633,13 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B75" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C75" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D75">
         <v>1959</v>
@@ -6648,13 +6648,13 @@
         <v>438</v>
       </c>
       <c r="I75" t="s">
+        <v>798</v>
+      </c>
+      <c r="J75" t="s">
         <v>799</v>
       </c>
-      <c r="J75" t="s">
-        <v>800</v>
-      </c>
       <c r="K75" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M75" t="s">
         <v>79</v>
@@ -6665,19 +6665,19 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B76" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C76" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D76">
         <v>2019</v>
       </c>
       <c r="E76" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F76" t="s">
         <v>38</v>
@@ -6686,10 +6686,10 @@
         <v>21</v>
       </c>
       <c r="I76" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J76" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="M76" t="s">
         <v>79</v>
@@ -6697,13 +6697,13 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B77" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C77" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D77">
         <v>1965</v>
@@ -6712,7 +6712,7 @@
         <v>51</v>
       </c>
       <c r="I77" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M77" t="s">
         <v>79</v>
@@ -6723,13 +6723,13 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B78" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C78" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D78">
         <v>1975</v>
@@ -6746,13 +6746,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B79" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C79" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F79" t="s">
         <v>51</v>
@@ -6763,28 +6763,28 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B80" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C80" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D80">
         <v>1960</v>
       </c>
       <c r="E80" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F80" t="s">
         <v>51</v>
       </c>
       <c r="I80" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K80" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M80" t="s">
         <v>79</v>
@@ -6795,13 +6795,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B81" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C81" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D81">
         <v>1956</v>
@@ -6810,7 +6810,7 @@
         <v>51</v>
       </c>
       <c r="I81" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M81" t="s">
         <v>79</v>
@@ -6818,13 +6818,13 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B82" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C82" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F82" t="s">
         <v>51</v>
@@ -6835,13 +6835,13 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B83" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C83" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D83">
         <v>1970</v>
@@ -6853,18 +6853,18 @@
         <v>79</v>
       </c>
       <c r="P83" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B84" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C84" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D84">
         <v>1976</v>
@@ -6881,13 +6881,13 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B85" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C85" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F85" t="s">
         <v>51</v>
@@ -6898,13 +6898,13 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B86" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F86" t="s">
         <v>51</v>
@@ -6915,13 +6915,13 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B87" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C87" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D87">
         <v>2007</v>
@@ -6935,13 +6935,13 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B88" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C88" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F88" t="s">
         <v>51</v>
@@ -6952,13 +6952,13 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B89" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C89" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F89" t="s">
         <v>51</v>
@@ -6969,13 +6969,13 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B90" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C90" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F90" t="s">
         <v>51</v>
@@ -6986,13 +6986,13 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B91" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C91" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D91">
         <v>1966</v>
@@ -7009,13 +7009,13 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C92" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D92">
         <v>1963</v>
@@ -7024,7 +7024,7 @@
         <v>51</v>
       </c>
       <c r="I92" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="M92" t="s">
         <v>79</v>
@@ -7035,13 +7035,13 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B93" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C93" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F93" t="s">
         <v>51</v>
@@ -7055,13 +7055,13 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B94" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C94" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D94">
         <v>1980</v>
@@ -7070,24 +7070,24 @@
         <v>79</v>
       </c>
       <c r="P94" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B95" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C95" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D95">
         <v>2014</v>
       </c>
       <c r="E95" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="M95" t="s">
         <v>79</v>
@@ -7095,13 +7095,13 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B96" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C96" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D96">
         <v>1990</v>
@@ -7115,22 +7115,22 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B97" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C97" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D97">
         <v>1985</v>
       </c>
       <c r="I97" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="J97" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M97" t="s">
         <v>79</v>
@@ -7141,13 +7141,13 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B98" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C98" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D98">
         <v>1974</v>
@@ -7156,24 +7156,24 @@
         <v>51</v>
       </c>
       <c r="L98" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M98" t="s">
         <v>79</v>
       </c>
       <c r="P98" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B99" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C99" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D99">
         <v>2014</v>
@@ -7187,28 +7187,28 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B100" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C100" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D100">
         <v>1978</v>
       </c>
       <c r="E100" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F100" t="s">
         <v>51</v>
       </c>
       <c r="I100" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J100" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M100" t="s">
         <v>79</v>
@@ -7217,18 +7217,18 @@
         <v>123</v>
       </c>
       <c r="P100" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B101" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C101" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D101">
         <v>1965</v>
@@ -7237,7 +7237,7 @@
         <v>51</v>
       </c>
       <c r="I101" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="M101" t="s">
         <v>79</v>
@@ -7246,18 +7246,18 @@
         <v>123</v>
       </c>
       <c r="P101" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B102" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C102" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F102" t="s">
         <v>51</v>
@@ -7271,13 +7271,13 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B103" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C103" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D103">
         <v>1982</v>
@@ -7286,7 +7286,7 @@
         <v>51</v>
       </c>
       <c r="I103" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="M103" t="s">
         <v>79</v>
@@ -7300,13 +7300,13 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B104" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C104" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D104">
         <v>1985</v>
@@ -7323,13 +7323,13 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B105" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C105" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F105" t="s">
         <v>51</v>
@@ -7343,13 +7343,13 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B106" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C106" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F106" t="s">
         <v>51</v>
@@ -7363,13 +7363,13 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B107" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C107" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F107" t="s">
         <v>51</v>
@@ -7383,13 +7383,13 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B108" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C108" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F108" t="s">
         <v>51</v>
@@ -7403,13 +7403,13 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B109" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C109" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F109" t="s">
         <v>51</v>
@@ -7423,13 +7423,13 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B110" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C110" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D110">
         <v>1984</v>
@@ -7438,7 +7438,7 @@
         <v>51</v>
       </c>
       <c r="I110" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="M110" t="s">
         <v>79</v>
@@ -7447,30 +7447,30 @@
         <v>123</v>
       </c>
       <c r="P110" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B111" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C111" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D111">
         <v>1983</v>
       </c>
       <c r="E111" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F111" t="s">
         <v>51</v>
       </c>
       <c r="I111" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M111" t="s">
         <v>79</v>
@@ -7481,13 +7481,13 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B112" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C112" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F112" t="s">
         <v>51</v>
@@ -7501,19 +7501,19 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B113" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C113" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D113">
         <v>1980</v>
       </c>
       <c r="E113" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F113" t="s">
         <v>51</v>
@@ -7530,13 +7530,13 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B114" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C114" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D114">
         <v>1985</v>
@@ -7545,7 +7545,7 @@
         <v>51</v>
       </c>
       <c r="I114" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="M114" t="s">
         <v>79</v>
@@ -7556,13 +7556,13 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B115" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C115" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F115" t="s">
         <v>51</v>
@@ -7576,13 +7576,13 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B116" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C116" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F116" t="s">
         <v>51</v>
@@ -7593,25 +7593,25 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B117" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C117" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D117">
         <v>2015</v>
       </c>
       <c r="E117" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F117" t="s">
         <v>51</v>
       </c>
       <c r="I117" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="M117" t="s">
         <v>79</v>
@@ -7619,19 +7619,19 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B118" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C118" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D118">
         <v>2019</v>
       </c>
       <c r="E118" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F118" t="s">
         <v>38</v>
@@ -7642,10 +7642,10 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B119" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D119">
         <v>2013</v>
@@ -7654,7 +7654,7 @@
         <v>51</v>
       </c>
       <c r="I119" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M119" t="s">
         <v>53</v>
@@ -7665,13 +7665,13 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B120" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C120" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D120">
         <v>2022</v>
@@ -7685,16 +7685,16 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B121" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D121">
         <v>2015</v>
       </c>
       <c r="E121" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F121" t="s">
         <v>38</v>
@@ -7708,25 +7708,25 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B122" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C122" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D122">
         <v>1955</v>
       </c>
       <c r="E122" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F122" t="s">
         <v>51</v>
       </c>
       <c r="I122" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="M122" t="s">
         <v>79</v>
@@ -7740,19 +7740,19 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B123" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C123" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D123">
         <v>2018</v>
       </c>
       <c r="E123" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F123" t="s">
         <v>38</v>
@@ -7763,19 +7763,19 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B124" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C124" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D124">
         <v>2007</v>
       </c>
       <c r="E124" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F124" t="s">
         <v>38</v>
@@ -7786,10 +7786,10 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B125" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D125">
         <v>2010</v>
@@ -7801,7 +7801,7 @@
         <v>38</v>
       </c>
       <c r="I125" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="M125" t="s">
         <v>45</v>
@@ -7809,25 +7809,25 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B126" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C126" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D126">
         <v>1988</v>
       </c>
       <c r="E126" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F126" t="s">
         <v>51</v>
       </c>
       <c r="I126" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="M126" t="s">
         <v>79</v>
@@ -7835,13 +7835,13 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B127" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C127" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D127">
         <v>2014</v>
@@ -7850,10 +7850,10 @@
         <v>38</v>
       </c>
       <c r="I127" t="s">
+        <v>965</v>
+      </c>
+      <c r="J127" t="s">
         <v>966</v>
-      </c>
-      <c r="J127" t="s">
-        <v>967</v>
       </c>
       <c r="M127" t="s">
         <v>79</v>
@@ -7861,19 +7861,19 @@
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B128" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C128" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D128">
         <v>2011</v>
       </c>
       <c r="E128" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="s">
         <v>38</v>
@@ -7884,19 +7884,19 @@
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B129" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C129" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D129">
         <v>2010</v>
       </c>
       <c r="E129" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F129" t="s">
         <v>38</v>
@@ -7907,13 +7907,13 @@
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B130" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C130" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D130">
         <v>1939</v>
@@ -7922,7 +7922,7 @@
         <v>51</v>
       </c>
       <c r="I130" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="M130" t="s">
         <v>79</v>
@@ -7930,13 +7930,13 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B131" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C131" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D131">
         <v>1939</v>
@@ -7945,7 +7945,7 @@
         <v>51</v>
       </c>
       <c r="I131" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="M131" t="s">
         <v>79</v>
@@ -7953,13 +7953,13 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B132" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C132" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D132">
         <v>1939</v>
@@ -7968,7 +7968,7 @@
         <v>51</v>
       </c>
       <c r="I132" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="M132" t="s">
         <v>79</v>
@@ -7976,13 +7976,13 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B133" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C133" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D133">
         <v>1939</v>
@@ -7991,7 +7991,7 @@
         <v>51</v>
       </c>
       <c r="I133" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="M133" t="s">
         <v>79</v>
@@ -7999,13 +7999,13 @@
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B134" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C134" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D134">
         <v>1939</v>
@@ -8014,7 +8014,7 @@
         <v>51</v>
       </c>
       <c r="I134" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="M134" t="s">
         <v>79</v>
@@ -8022,13 +8022,13 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B135" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C135" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D135">
         <v>1955</v>
@@ -8042,42 +8042,42 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B136" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C136" t="s">
         <v>1123</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1124</v>
       </c>
       <c r="D136">
         <v>1953</v>
       </c>
       <c r="E136" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="F136" t="s">
         <v>38</v>
       </c>
       <c r="I136" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="M136" t="s">
         <v>79</v>
       </c>
       <c r="P136" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B137" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C137" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F137" t="s">
         <v>51</v>
@@ -8086,18 +8086,18 @@
         <v>79</v>
       </c>
       <c r="P137" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B138" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C138" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F138" t="s">
         <v>51</v>
@@ -8108,13 +8108,13 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B139" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C139" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F139" t="s">
         <v>51</v>
@@ -9501,7 +9501,7 @@
         <v>194</v>
       </c>
       <c r="G50" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -9608,7 +9608,7 @@
         <v>462</v>
       </c>
       <c r="D57" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E57">
         <v>1912</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B79" t="s">
         <v>566</v>
@@ -9924,7 +9924,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B80" t="s">
         <v>567</v>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B81" t="s">
         <v>568</v>
@@ -9955,10 +9955,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B82" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C82" t="s">
         <v>580</v>
@@ -9978,7 +9978,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B83" t="s">
         <v>572</v>
@@ -9995,7 +9995,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B84" t="s">
         <v>573</v>
@@ -10012,7 +10012,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B85" t="s">
         <v>574</v>
@@ -10029,7 +10029,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B86" t="s">
         <v>582</v>
@@ -10043,7 +10043,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B87" t="s">
         <v>583</v>
@@ -10057,7 +10057,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B88" t="s">
         <v>598</v>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B89" t="s">
         <v>590</v>
@@ -10097,7 +10097,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B90" t="s">
         <v>591</v>
@@ -10114,13 +10114,13 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B91" t="s">
         <v>601</v>
       </c>
       <c r="C91" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D91" t="s">
         <v>194</v>
@@ -10128,10 +10128,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B92" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D92" t="s">
         <v>190</v>
@@ -10139,10 +10139,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B93" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D93" t="s">
         <v>190</v>
@@ -10150,13 +10150,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B94" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C94" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D94" t="s">
         <v>23</v>
@@ -10164,13 +10164,13 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B95" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C95" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D95" t="s">
         <v>24</v>
@@ -10178,13 +10178,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B96" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C96" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D96" t="s">
         <v>190</v>
@@ -10192,13 +10192,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B97" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C97" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D97" t="s">
         <v>190</v>
@@ -10206,13 +10206,13 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B98" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C98" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D98" t="s">
         <v>190</v>
@@ -10220,13 +10220,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B99" t="s">
+        <v>618</v>
+      </c>
+      <c r="C99" t="s">
         <v>619</v>
-      </c>
-      <c r="C99" t="s">
-        <v>620</v>
       </c>
       <c r="D99" t="s">
         <v>190</v>
@@ -10234,13 +10234,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B100" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C100" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D100" t="s">
         <v>23</v>
@@ -10257,13 +10257,13 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B101" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C101" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D101" t="s">
         <v>23</v>
@@ -10271,13 +10271,13 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B102" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C102" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D102" t="s">
         <v>23</v>
@@ -10285,13 +10285,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B103" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C103" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D103" t="s">
         <v>23</v>
@@ -10299,13 +10299,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B104" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C104" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D104" t="s">
         <v>24</v>
@@ -10313,13 +10313,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B105" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C105" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D105" t="s">
         <v>190</v>
@@ -10327,13 +10327,13 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B106" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C106" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D106" t="s">
         <v>190</v>
@@ -10341,13 +10341,13 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B107" t="s">
+        <v>640</v>
+      </c>
+      <c r="C107" t="s">
         <v>641</v>
-      </c>
-      <c r="C107" t="s">
-        <v>642</v>
       </c>
       <c r="D107" t="s">
         <v>190</v>
@@ -10355,13 +10355,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B108" t="s">
+        <v>692</v>
+      </c>
+      <c r="C108" t="s">
         <v>693</v>
-      </c>
-      <c r="C108" t="s">
-        <v>694</v>
       </c>
       <c r="D108" t="s">
         <v>23</v>
@@ -10378,13 +10378,13 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B109" t="s">
+        <v>703</v>
+      </c>
+      <c r="C109" t="s">
         <v>704</v>
-      </c>
-      <c r="C109" t="s">
-        <v>705</v>
       </c>
       <c r="D109" t="s">
         <v>23</v>
@@ -10395,13 +10395,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B110" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C110" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D110" t="s">
         <v>23</v>
@@ -10412,13 +10412,13 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B111" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C111" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D111" t="s">
         <v>23</v>
@@ -10429,13 +10429,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B112" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C112" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D112" t="s">
         <v>24</v>
@@ -10446,13 +10446,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B113" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C113" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D113" t="s">
         <v>190</v>
@@ -10463,13 +10463,13 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B114" t="s">
+        <v>713</v>
+      </c>
+      <c r="C114" t="s">
         <v>714</v>
-      </c>
-      <c r="C114" t="s">
-        <v>715</v>
       </c>
       <c r="D114" t="s">
         <v>190</v>
@@ -10480,13 +10480,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B115" t="s">
+        <v>742</v>
+      </c>
+      <c r="C115" t="s">
         <v>743</v>
-      </c>
-      <c r="C115" t="s">
-        <v>744</v>
       </c>
       <c r="D115" t="s">
         <v>23</v>
@@ -10497,13 +10497,13 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B116" t="s">
+        <v>745</v>
+      </c>
+      <c r="C116" t="s">
         <v>746</v>
-      </c>
-      <c r="C116" t="s">
-        <v>747</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -10514,13 +10514,13 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B117" t="s">
+        <v>747</v>
+      </c>
+      <c r="C117" t="s">
         <v>748</v>
-      </c>
-      <c r="C117" t="s">
-        <v>749</v>
       </c>
       <c r="D117" t="s">
         <v>23</v>
@@ -10531,13 +10531,13 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B118" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C118" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D118" t="s">
         <v>23</v>
@@ -10548,13 +10548,13 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B119" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C119" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D119" t="s">
         <v>24</v>
@@ -10565,13 +10565,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B120" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C120" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D120" t="s">
         <v>24</v>
@@ -10582,13 +10582,13 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B121" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C121" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D121" t="s">
         <v>190</v>
@@ -10596,13 +10596,13 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B122" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C122" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D122" t="s">
         <v>190</v>
@@ -10610,13 +10610,13 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B123" t="s">
+        <v>771</v>
+      </c>
+      <c r="C123" t="s">
         <v>772</v>
-      </c>
-      <c r="C123" t="s">
-        <v>773</v>
       </c>
       <c r="D123" t="s">
         <v>190</v>
@@ -10624,13 +10624,13 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B124" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C124" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D124" t="s">
         <v>23</v>
@@ -10638,13 +10638,13 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B125" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C125" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D125" t="s">
         <v>194</v>
@@ -10652,13 +10652,13 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B126" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C126" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D126" t="s">
         <v>190</v>
@@ -10666,13 +10666,13 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B127" t="s">
+        <v>781</v>
+      </c>
+      <c r="C127" t="s">
         <v>782</v>
-      </c>
-      <c r="C127" t="s">
-        <v>783</v>
       </c>
       <c r="D127" t="s">
         <v>190</v>
@@ -10680,13 +10680,13 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B128" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C128" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D128" t="s">
         <v>23</v>
@@ -10694,13 +10694,13 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B129" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C129" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D129" t="s">
         <v>24</v>
@@ -10708,13 +10708,13 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B130" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C130" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D130" t="s">
         <v>190</v>
@@ -10722,13 +10722,13 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B131" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C131" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D131" t="s">
         <v>190</v>
@@ -10736,13 +10736,13 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B132" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C132" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D132" t="s">
         <v>190</v>
@@ -10750,13 +10750,13 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B133" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C133" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D133" t="s">
         <v>190</v>
@@ -10764,13 +10764,13 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B134" t="s">
+        <v>804</v>
+      </c>
+      <c r="C134" t="s">
         <v>805</v>
-      </c>
-      <c r="C134" t="s">
-        <v>806</v>
       </c>
       <c r="D134" t="s">
         <v>190</v>
@@ -10778,10 +10778,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B135" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D135" t="s">
         <v>23</v>
@@ -10789,13 +10789,13 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B136" t="s">
+        <v>818</v>
+      </c>
+      <c r="C136" t="s">
         <v>819</v>
-      </c>
-      <c r="C136" t="s">
-        <v>820</v>
       </c>
       <c r="D136" t="s">
         <v>23</v>
@@ -10812,13 +10812,13 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B137" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C137" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D137" t="s">
         <v>190</v>
@@ -10829,13 +10829,13 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B138" t="s">
+        <v>826</v>
+      </c>
+      <c r="C138" t="s">
         <v>827</v>
-      </c>
-      <c r="C138" t="s">
-        <v>828</v>
       </c>
       <c r="D138" t="s">
         <v>190</v>
@@ -10846,13 +10846,13 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B139" t="s">
+        <v>830</v>
+      </c>
+      <c r="C139" t="s">
         <v>831</v>
-      </c>
-      <c r="C139" t="s">
-        <v>832</v>
       </c>
       <c r="D139" t="s">
         <v>23</v>
@@ -10863,13 +10863,13 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B140" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C140" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D140" t="s">
         <v>23</v>
@@ -10883,13 +10883,13 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B141" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C141" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D141" t="s">
         <v>23</v>
@@ -10900,13 +10900,13 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B142" t="s">
+        <v>850</v>
+      </c>
+      <c r="C142" t="s">
         <v>851</v>
-      </c>
-      <c r="C142" t="s">
-        <v>852</v>
       </c>
       <c r="D142" t="s">
         <v>23</v>
@@ -10917,13 +10917,13 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B143" t="s">
+        <v>863</v>
+      </c>
+      <c r="C143" t="s">
         <v>864</v>
-      </c>
-      <c r="C143" t="s">
-        <v>865</v>
       </c>
       <c r="D143" t="s">
         <v>194</v>
@@ -10937,13 +10937,13 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B144" t="s">
+        <v>870</v>
+      </c>
+      <c r="C144" t="s">
         <v>871</v>
-      </c>
-      <c r="C144" t="s">
-        <v>872</v>
       </c>
       <c r="D144" t="s">
         <v>194</v>
@@ -10954,13 +10954,13 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B145" t="s">
+        <v>917</v>
+      </c>
+      <c r="C145" t="s">
         <v>918</v>
-      </c>
-      <c r="C145" t="s">
-        <v>919</v>
       </c>
       <c r="D145" t="s">
         <v>23</v>
@@ -10968,13 +10968,13 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B146" t="s">
+        <v>922</v>
+      </c>
+      <c r="C146" t="s">
         <v>923</v>
-      </c>
-      <c r="C146" t="s">
-        <v>924</v>
       </c>
       <c r="D146" t="s">
         <v>194</v>
@@ -10982,13 +10982,13 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B147" t="s">
+        <v>924</v>
+      </c>
+      <c r="C147" t="s">
         <v>925</v>
-      </c>
-      <c r="C147" t="s">
-        <v>926</v>
       </c>
       <c r="D147" t="s">
         <v>23</v>
@@ -10996,10 +10996,10 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B148" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D148" t="s">
         <v>23</v>
@@ -11007,13 +11007,13 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B149" t="s">
+        <v>941</v>
+      </c>
+      <c r="C149" t="s">
         <v>942</v>
-      </c>
-      <c r="C149" t="s">
-        <v>943</v>
       </c>
       <c r="D149" t="s">
         <v>23</v>
@@ -11022,15 +11022,15 @@
         <v>1929</v>
       </c>
       <c r="G149" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B150" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D150" t="s">
         <v>23</v>
@@ -11038,13 +11038,13 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B151" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C151" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D151" t="s">
         <v>23</v>
@@ -11052,13 +11052,13 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B152" t="s">
+        <v>958</v>
+      </c>
+      <c r="C152" t="s">
         <v>959</v>
-      </c>
-      <c r="C152" t="s">
-        <v>960</v>
       </c>
       <c r="D152" t="s">
         <v>23</v>
@@ -11066,13 +11066,13 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B153" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C153" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D153" t="s">
         <v>23</v>
@@ -11080,13 +11080,13 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B154" t="s">
+        <v>966</v>
+      </c>
+      <c r="C154" t="s">
         <v>967</v>
-      </c>
-      <c r="C154" t="s">
-        <v>968</v>
       </c>
       <c r="D154" t="s">
         <v>24</v>
@@ -11094,13 +11094,13 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B155" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C155" t="s">
         <v>1119</v>
-      </c>
-      <c r="C155" t="s">
-        <v>1120</v>
       </c>
       <c r="D155" t="s">
         <v>23</v>
@@ -11108,13 +11108,13 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B156" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C156" t="s">
         <v>1126</v>
-      </c>
-      <c r="C156" t="s">
-        <v>1127</v>
       </c>
       <c r="D156" t="s">
         <v>23</v>
@@ -11637,7 +11637,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B25" t="s">
         <v>585</v>
@@ -11651,7 +11651,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B26" t="s">
         <v>587</v>
@@ -11668,13 +11668,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B27" t="s">
+        <v>607</v>
+      </c>
+      <c r="C27" t="s">
         <v>608</v>
-      </c>
-      <c r="C27" t="s">
-        <v>609</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -11682,13 +11682,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B28" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C28" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D28" t="s">
         <v>79</v>
@@ -11696,13 +11696,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B29" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C29" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D29" t="s">
         <v>79</v>
@@ -11710,13 +11710,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B30" t="s">
+        <v>722</v>
+      </c>
+      <c r="C30" t="s">
         <v>723</v>
-      </c>
-      <c r="C30" t="s">
-        <v>724</v>
       </c>
       <c r="D30" t="s">
         <v>79</v>
@@ -11724,13 +11724,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B31" t="s">
+        <v>760</v>
+      </c>
+      <c r="C31" t="s">
         <v>761</v>
-      </c>
-      <c r="C31" t="s">
-        <v>762</v>
       </c>
       <c r="D31" t="s">
         <v>79</v>
@@ -11738,13 +11738,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B32" t="s">
+        <v>834</v>
+      </c>
+      <c r="C32" t="s">
         <v>835</v>
-      </c>
-      <c r="C32" t="s">
-        <v>836</v>
       </c>
       <c r="D32" t="s">
         <v>79</v>
@@ -11752,13 +11752,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="C33" t="s">
         <v>857</v>
-      </c>
-      <c r="C33" t="s">
-        <v>858</v>
       </c>
       <c r="D33" t="s">
         <v>79</v>
@@ -11766,13 +11766,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B34" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C34" t="s">
         <v>1147</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1148</v>
       </c>
       <c r="D34" t="s">
         <v>79</v>
